--- a/Datasets/TestDataUtilities_Transformer_Health_210pts.xlsx
+++ b/Datasets/TestDataUtilities_Transformer_Health_210pts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://techsource-my.sharepoint.com/personal/kantika_ascendas-asia_com/Documents/Documents/1.Kantika/Demo/EGAT/Utilities-AI-Asset-Analytics/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{29E2A1A2-60EC-4907-882E-D20FC4EA8FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F2C3D06-D137-48F5-823C-8F74E119E261}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{61595CDF-CD3A-4503-99F1-5986FCF2C475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8527EA3D-F882-4855-89C9-57134E17650A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TransformerHealth" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="67">
   <si>
     <t>SubstationID</t>
   </si>
@@ -64,6 +64,9 @@
     <t>TR-015</t>
   </si>
   <si>
+    <t>SS-01</t>
+  </si>
+  <si>
     <t>TR-022</t>
   </si>
   <si>
@@ -77,6 +80,9 @@
   </si>
   <si>
     <t>SS-14</t>
+  </si>
+  <si>
+    <t>TR-003</t>
   </si>
   <si>
     <t>SS-09</t>
@@ -107,6 +113,9 @@
   </si>
   <si>
     <t>TR-030</t>
+  </si>
+  <si>
+    <t>TR-005</t>
   </si>
   <si>
     <t>TR-035</t>
@@ -148,6 +157,9 @@
     <t>TR-032</t>
   </si>
   <si>
+    <t>TR-006</t>
+  </si>
+  <si>
     <t>SS-06</t>
   </si>
   <si>
@@ -172,10 +184,16 @@
     <t>TR-012</t>
   </si>
   <si>
+    <t>TR-023</t>
+  </si>
+  <si>
     <t>TR-027</t>
   </si>
   <si>
     <t>TR-018</t>
+  </si>
+  <si>
+    <t>TR-028</t>
   </si>
   <si>
     <t>TR-036</t>
@@ -184,7 +202,25 @@
     <t>TR-007</t>
   </si>
   <si>
+    <t>TR-029</t>
+  </si>
+  <si>
+    <t>TR-004</t>
+  </si>
+  <si>
+    <t>TR-039</t>
+  </si>
+  <si>
     <t>TR-020</t>
+  </si>
+  <si>
+    <t>TR-031</t>
+  </si>
+  <si>
+    <t>TR-016</t>
+  </si>
+  <si>
+    <t>TR-019</t>
   </si>
 </sst>
 </file>
@@ -528,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.33203125" customWidth="1"/>
@@ -584,1864 +620,7982 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>230</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="F2">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="G2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="I2">
-        <v>118</v>
+        <v>830</v>
       </c>
       <c r="J2">
-        <v>429</v>
+        <v>857</v>
       </c>
       <c r="K2">
-        <v>63</v>
+        <v>216</v>
       </c>
       <c r="L2">
-        <v>1.84</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C3">
-        <v>500</v>
+        <v>115</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="F3">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="G3">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="I3">
-        <v>99</v>
+        <v>401</v>
       </c>
       <c r="J3">
-        <v>231</v>
+        <v>913</v>
       </c>
       <c r="K3">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="L3">
-        <v>2.46</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="C4">
-        <v>500</v>
+        <v>115</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="F4">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="G4">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H4">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="I4">
-        <v>248</v>
+        <v>135</v>
       </c>
       <c r="J4">
-        <v>790</v>
+        <v>530</v>
       </c>
       <c r="K4">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="L4">
-        <v>4.57</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
-        <v>36</v>
-      </c>
       <c r="C5">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="E5">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F5">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G5">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H5">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I5">
-        <v>212</v>
+        <v>718</v>
       </c>
       <c r="J5">
-        <v>876</v>
+        <v>1835</v>
       </c>
       <c r="K5">
-        <v>105</v>
+        <v>470</v>
       </c>
       <c r="L5">
-        <v>3.43</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C6">
-        <v>115</v>
+        <v>500</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E6">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F6">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="G6">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H6">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="I6">
-        <v>369</v>
+        <v>975</v>
       </c>
       <c r="J6">
-        <v>1205</v>
+        <v>1413</v>
       </c>
       <c r="K6">
-        <v>327</v>
+        <v>215</v>
       </c>
       <c r="L6">
-        <v>9.4600000000000009</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C7">
-        <v>500</v>
+        <v>115</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E7">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F7">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="G7">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I7">
-        <v>861</v>
+        <v>201</v>
       </c>
       <c r="J7">
-        <v>1393</v>
+        <v>815</v>
       </c>
       <c r="K7">
-        <v>229</v>
+        <v>148</v>
       </c>
       <c r="L7">
-        <v>9.76</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>230</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="F8">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="G8">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="I8">
-        <v>92</v>
+        <v>947</v>
       </c>
       <c r="J8">
-        <v>259</v>
+        <v>1110</v>
       </c>
       <c r="K8">
-        <v>30</v>
+        <v>279</v>
       </c>
       <c r="L8">
-        <v>2.69</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C9">
         <v>500</v>
       </c>
       <c r="D9">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E9">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F9">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="G9">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H9">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="I9">
-        <v>731</v>
+        <v>673</v>
       </c>
       <c r="J9">
-        <v>854</v>
+        <v>1777</v>
       </c>
       <c r="K9">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L9">
-        <v>8.3699999999999992</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C10">
-        <v>115</v>
+        <v>230</v>
       </c>
       <c r="D10">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E10">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="F10">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="G10">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="H10">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>652</v>
+        <v>95</v>
       </c>
       <c r="J10">
-        <v>1061</v>
+        <v>289</v>
       </c>
       <c r="K10">
-        <v>416</v>
+        <v>58</v>
       </c>
       <c r="L10">
-        <v>8.23</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C11">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="D11">
+        <v>31</v>
+      </c>
+      <c r="E11">
+        <v>101</v>
+      </c>
+      <c r="F11">
+        <v>92</v>
+      </c>
+      <c r="G11">
         <v>34</v>
       </c>
-      <c r="E11">
-        <v>119</v>
-      </c>
-      <c r="F11">
-        <v>99</v>
-      </c>
-      <c r="G11">
-        <v>32</v>
-      </c>
       <c r="H11">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="I11">
-        <v>816</v>
+        <v>459</v>
       </c>
       <c r="J11">
-        <v>1043</v>
+        <v>1779</v>
       </c>
       <c r="K11">
-        <v>248</v>
+        <v>485</v>
       </c>
       <c r="L11">
-        <v>9.3000000000000007</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C12">
-        <v>230</v>
+        <v>115</v>
       </c>
       <c r="D12">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F12">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G12">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H12">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="I12">
-        <v>116</v>
+        <v>331</v>
       </c>
       <c r="J12">
-        <v>560</v>
+        <v>771</v>
       </c>
       <c r="K12">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="L12">
-        <v>4.28</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C13">
-        <v>230</v>
+        <v>115</v>
       </c>
       <c r="D13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E13">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="F13">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G13">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H13">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I13">
-        <v>168</v>
+        <v>986</v>
       </c>
       <c r="J13">
-        <v>551</v>
+        <v>1252</v>
       </c>
       <c r="K13">
-        <v>122</v>
+        <v>425</v>
       </c>
       <c r="L13">
-        <v>4.67</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14">
+        <v>115</v>
+      </c>
+      <c r="D14">
         <v>14</v>
       </c>
-      <c r="C14">
-        <v>500</v>
-      </c>
-      <c r="D14">
-        <v>13</v>
-      </c>
       <c r="E14">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="F14">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G14">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H14">
         <v>36</v>
       </c>
       <c r="I14">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="J14">
-        <v>649</v>
+        <v>739</v>
       </c>
       <c r="K14">
-        <v>199</v>
+        <v>68</v>
       </c>
       <c r="L14">
-        <v>4.18</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C15">
-        <v>115</v>
+        <v>230</v>
       </c>
       <c r="D15">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E15">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F15">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="G15">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="H15">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I15">
-        <v>172</v>
+        <v>34</v>
       </c>
       <c r="J15">
-        <v>915</v>
+        <v>473</v>
       </c>
       <c r="K15">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L15">
-        <v>3.06</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C16">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="D16">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E16">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="F16">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="G16">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H16">
-        <v>93</v>
+        <v>5</v>
       </c>
       <c r="I16">
-        <v>957</v>
+        <v>83</v>
       </c>
       <c r="J16">
-        <v>1907</v>
+        <v>113</v>
       </c>
       <c r="K16">
-        <v>437</v>
+        <v>43</v>
       </c>
       <c r="L16">
-        <v>8.18</v>
+        <v>2.2200000000000002</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17">
+        <v>500</v>
+      </c>
+      <c r="D17">
+        <v>6</v>
+      </c>
+      <c r="E17">
         <v>43</v>
       </c>
-      <c r="C17">
-        <v>230</v>
-      </c>
-      <c r="D17">
-        <v>12</v>
-      </c>
-      <c r="E17">
-        <v>62</v>
-      </c>
       <c r="F17">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G17">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H17">
         <v>6</v>
       </c>
       <c r="I17">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="J17">
-        <v>391</v>
+        <v>179</v>
       </c>
       <c r="K17">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="L17">
-        <v>2.1</v>
+        <v>2.5499999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
         <v>25</v>
       </c>
       <c r="C18">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="D18">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="E18">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="F18">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="G18">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H18">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="I18">
-        <v>880</v>
+        <v>300</v>
       </c>
       <c r="J18">
-        <v>1461</v>
+        <v>748</v>
       </c>
       <c r="K18">
-        <v>355</v>
+        <v>64</v>
       </c>
       <c r="L18">
-        <v>11.21</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
         <v>34</v>
       </c>
-      <c r="B19" t="s">
-        <v>45</v>
-      </c>
       <c r="C19">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="D19">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E19">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="F19">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="G19">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H19">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I19">
-        <v>297</v>
+        <v>335</v>
       </c>
       <c r="J19">
-        <v>976</v>
+        <v>1560</v>
       </c>
       <c r="K19">
-        <v>84</v>
+        <v>436</v>
       </c>
       <c r="L19">
-        <v>2.66</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C20">
-        <v>500</v>
+        <v>115</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E20">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F20">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="G20">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H20">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="I20">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="J20">
-        <v>402</v>
+        <v>825</v>
       </c>
       <c r="K20">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L20">
-        <v>2</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C21">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="D21">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E21">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F21">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G21">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H21">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="I21">
-        <v>315</v>
+        <v>118</v>
       </c>
       <c r="J21">
-        <v>776</v>
+        <v>429</v>
       </c>
       <c r="K21">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="L21">
-        <v>4.9800000000000004</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C22">
         <v>500</v>
       </c>
       <c r="D22">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E22">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="F22">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="G22">
         <v>28</v>
       </c>
       <c r="H22">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="I22">
-        <v>326</v>
+        <v>99</v>
       </c>
       <c r="J22">
-        <v>801</v>
+        <v>231</v>
       </c>
       <c r="K22">
-        <v>136</v>
+        <v>17</v>
       </c>
       <c r="L22">
-        <v>5.48</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C23">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="D23">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E23">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="F23">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="G23">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H23">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="I23">
-        <v>619</v>
+        <v>248</v>
       </c>
       <c r="J23">
-        <v>1120</v>
+        <v>790</v>
       </c>
       <c r="K23">
-        <v>217</v>
+        <v>96</v>
       </c>
       <c r="L23">
-        <v>8.41</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C24">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="D24">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E24">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="F24">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="G24">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H24">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="I24">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J24">
-        <v>672</v>
+        <v>876</v>
       </c>
       <c r="K24">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="L24">
-        <v>5.43</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C25">
-        <v>500</v>
+        <v>115</v>
       </c>
       <c r="D25">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E25">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="F25">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="G25">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H25">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="I25">
-        <v>84</v>
+        <v>369</v>
       </c>
       <c r="J25">
-        <v>146</v>
+        <v>1205</v>
       </c>
       <c r="K25">
-        <v>71</v>
+        <v>327</v>
       </c>
       <c r="L25">
-        <v>1.3</v>
+        <v>9.4600000000000009</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C26">
-        <v>115</v>
+        <v>500</v>
       </c>
       <c r="D26">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E26">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F26">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="G26">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H26">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I26">
-        <v>300</v>
+        <v>861</v>
       </c>
       <c r="J26">
-        <v>926</v>
+        <v>1393</v>
       </c>
       <c r="K26">
-        <v>179</v>
+        <v>229</v>
       </c>
       <c r="L26">
-        <v>3.67</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C27">
         <v>230</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E27">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F27">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G27">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H27">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="I27">
-        <v>137</v>
+        <v>92</v>
       </c>
       <c r="J27">
-        <v>143</v>
+        <v>259</v>
       </c>
       <c r="K27">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L27">
-        <v>2.2400000000000002</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C28">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E28">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="F28">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="G28">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H28">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="I28">
-        <v>146</v>
+        <v>731</v>
       </c>
       <c r="J28">
-        <v>100</v>
+        <v>854</v>
       </c>
       <c r="K28">
-        <v>35</v>
+        <v>244</v>
       </c>
       <c r="L28">
-        <v>0.89</v>
+        <v>8.3699999999999992</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C29">
-        <v>500</v>
+        <v>115</v>
       </c>
       <c r="D29">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E29">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F29">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="G29">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H29">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="I29">
-        <v>754</v>
+        <v>652</v>
       </c>
       <c r="J29">
-        <v>1456</v>
+        <v>1061</v>
       </c>
       <c r="K29">
-        <v>259</v>
+        <v>416</v>
       </c>
       <c r="L29">
-        <v>10.32</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30">
+        <v>115</v>
+      </c>
+      <c r="D30">
         <v>19</v>
       </c>
-      <c r="B30" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30">
-        <v>500</v>
-      </c>
-      <c r="D30">
-        <v>32</v>
-      </c>
       <c r="E30">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="F30">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="G30">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H30">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="I30">
-        <v>601</v>
+        <v>203</v>
       </c>
       <c r="J30">
-        <v>1259</v>
+        <v>507</v>
       </c>
       <c r="K30">
-        <v>295</v>
+        <v>181</v>
       </c>
       <c r="L30">
-        <v>7.63</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C31">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="D31">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E31">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="F31">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="G31">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="H31">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="I31">
-        <v>144</v>
+        <v>652</v>
       </c>
       <c r="J31">
-        <v>351</v>
+        <v>1768</v>
       </c>
       <c r="K31">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="L31">
-        <v>2.76</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C32">
         <v>500</v>
       </c>
       <c r="D32">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E32">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F32">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="G32">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H32">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="I32">
-        <v>367</v>
+        <v>93</v>
       </c>
       <c r="J32">
-        <v>775</v>
+        <v>486</v>
       </c>
       <c r="K32">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="L32">
-        <v>5.12</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C33">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E33">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="F33">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="G33">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H33">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I33">
-        <v>61</v>
+        <v>395</v>
       </c>
       <c r="J33">
-        <v>272</v>
+        <v>796</v>
       </c>
       <c r="K33">
-        <v>10</v>
+        <v>113</v>
       </c>
       <c r="L33">
-        <v>1.53</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C34">
         <v>230</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E34">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="F34">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="G34">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H34">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="I34">
-        <v>38</v>
+        <v>975</v>
       </c>
       <c r="J34">
-        <v>358</v>
+        <v>1248</v>
       </c>
       <c r="K34">
-        <v>59</v>
+        <v>415</v>
       </c>
       <c r="L34">
-        <v>0.71</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C35">
-        <v>500</v>
+        <v>115</v>
       </c>
       <c r="D35">
         <v>28</v>
       </c>
       <c r="E35">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F35">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="G35">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H35">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="I35">
-        <v>830</v>
+        <v>253</v>
       </c>
       <c r="J35">
-        <v>1537</v>
+        <v>896</v>
       </c>
       <c r="K35">
-        <v>465</v>
+        <v>65</v>
       </c>
       <c r="L35">
-        <v>7.76</v>
+        <v>5.0999999999999996</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C36">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="D36">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E36">
         <v>91</v>
       </c>
       <c r="F36">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G36">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H36">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I36">
-        <v>727</v>
+        <v>853</v>
       </c>
       <c r="J36">
-        <v>1289</v>
+        <v>1205</v>
       </c>
       <c r="K36">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="L36">
-        <v>5.47</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C37">
-        <v>230</v>
+        <v>115</v>
       </c>
       <c r="D37">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E37">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="F37">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="G37">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H37">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="I37">
-        <v>941</v>
+        <v>131</v>
       </c>
       <c r="J37">
-        <v>1924</v>
+        <v>246</v>
       </c>
       <c r="K37">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="L37">
-        <v>9.4600000000000009</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C38">
-        <v>115</v>
+        <v>500</v>
       </c>
       <c r="D38">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E38">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="F38">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G38">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H38">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="I38">
-        <v>459</v>
+        <v>579</v>
       </c>
       <c r="J38">
-        <v>1360</v>
+        <v>1812</v>
       </c>
       <c r="K38">
-        <v>305</v>
+        <v>483</v>
       </c>
       <c r="L38">
-        <v>6.05</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="C39">
-        <v>230</v>
+        <v>115</v>
       </c>
       <c r="D39">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E39">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="F39">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="G39">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H39">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="I39">
-        <v>879</v>
+        <v>74</v>
       </c>
       <c r="J39">
-        <v>1308</v>
+        <v>323</v>
       </c>
       <c r="K39">
-        <v>309</v>
+        <v>14</v>
       </c>
       <c r="L39">
-        <v>8.2200000000000006</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C40">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="E40">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="F40">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G40">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H40">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="I40">
-        <v>17</v>
+        <v>816</v>
       </c>
       <c r="J40">
-        <v>316</v>
+        <v>1043</v>
       </c>
       <c r="K40">
-        <v>17</v>
+        <v>248</v>
       </c>
       <c r="L40">
-        <v>1.7</v>
+        <v>9.3000000000000007</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41">
+        <v>230</v>
+      </c>
+      <c r="D41">
+        <v>20</v>
+      </c>
+      <c r="E41">
+        <v>76</v>
+      </c>
+      <c r="F41">
+        <v>82</v>
+      </c>
+      <c r="G41">
         <v>37</v>
       </c>
-      <c r="B41" t="s">
-        <v>50</v>
-      </c>
-      <c r="C41">
-        <v>500</v>
-      </c>
-      <c r="D41">
-        <v>7</v>
-      </c>
-      <c r="E41">
-        <v>66</v>
-      </c>
-      <c r="F41">
-        <v>67</v>
-      </c>
-      <c r="G41">
-        <v>27</v>
-      </c>
       <c r="H41">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I41">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="J41">
-        <v>473</v>
+        <v>560</v>
       </c>
       <c r="K41">
-        <v>12</v>
+        <v>106</v>
       </c>
       <c r="L41">
-        <v>2.67</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C42">
         <v>230</v>
       </c>
       <c r="D42">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E42">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F42">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G42">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H42">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I42">
-        <v>124</v>
+        <v>168</v>
       </c>
       <c r="J42">
-        <v>828</v>
+        <v>551</v>
       </c>
       <c r="K42">
-        <v>198</v>
+        <v>122</v>
       </c>
       <c r="L42">
-        <v>5.91</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="C43">
-        <v>115</v>
+        <v>500</v>
       </c>
       <c r="D43">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E43">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="F43">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="G43">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H43">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="I43">
-        <v>587</v>
+        <v>128</v>
       </c>
       <c r="J43">
-        <v>1160</v>
+        <v>649</v>
       </c>
       <c r="K43">
-        <v>279</v>
+        <v>199</v>
       </c>
       <c r="L43">
-        <v>10.51</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C44">
-        <v>500</v>
+        <v>115</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E44">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="F44">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="G44">
         <v>37</v>
       </c>
       <c r="H44">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="I44">
-        <v>44</v>
+        <v>172</v>
       </c>
       <c r="J44">
-        <v>441</v>
+        <v>915</v>
       </c>
       <c r="K44">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="L44">
-        <v>0.72</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C45">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="D45">
         <v>29</v>
       </c>
       <c r="E45">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="F45">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="G45">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="H45">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="I45">
-        <v>391</v>
+        <v>957</v>
       </c>
       <c r="J45">
-        <v>800</v>
+        <v>1907</v>
       </c>
       <c r="K45">
-        <v>180</v>
+        <v>437</v>
       </c>
       <c r="L45">
-        <v>5.48</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C46">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E46">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="F46">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G46">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H46">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I46">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="J46">
-        <v>445</v>
+        <v>391</v>
       </c>
       <c r="K46">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="L46">
-        <v>2.3199999999999998</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C47">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="D47">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E47">
+        <v>114</v>
+      </c>
+      <c r="F47">
         <v>116</v>
       </c>
-      <c r="F47">
-        <v>109</v>
-      </c>
       <c r="G47">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H47">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="I47">
-        <v>860</v>
+        <v>880</v>
       </c>
       <c r="J47">
-        <v>1141</v>
+        <v>1461</v>
       </c>
       <c r="K47">
-        <v>205</v>
+        <v>355</v>
       </c>
       <c r="L47">
-        <v>11.27</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B48" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C48">
         <v>500</v>
       </c>
       <c r="D48">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E48">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="F48">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="G48">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H48">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="I48">
-        <v>920</v>
+        <v>297</v>
       </c>
       <c r="J48">
-        <v>1569</v>
+        <v>976</v>
       </c>
       <c r="K48">
-        <v>300</v>
+        <v>84</v>
       </c>
       <c r="L48">
-        <v>9.82</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C49">
-        <v>115</v>
+        <v>500</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="F49">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G49">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H49">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I49">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="J49">
-        <v>157</v>
+        <v>402</v>
       </c>
       <c r="K49">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L49">
-        <v>2.61</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>24</v>
+      </c>
+      <c r="B50" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50">
+        <v>500</v>
+      </c>
+      <c r="D50">
+        <v>13</v>
+      </c>
+      <c r="E50">
+        <v>80</v>
+      </c>
+      <c r="F50">
+        <v>71</v>
+      </c>
+      <c r="G50">
+        <v>26</v>
+      </c>
+      <c r="H50">
+        <v>26</v>
+      </c>
+      <c r="I50">
+        <v>315</v>
+      </c>
+      <c r="J50">
+        <v>776</v>
+      </c>
+      <c r="K50">
+        <v>88</v>
+      </c>
+      <c r="L50">
+        <v>4.9800000000000004</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51">
+        <v>500</v>
+      </c>
+      <c r="D51">
+        <v>10</v>
+      </c>
+      <c r="E51">
+        <v>84</v>
+      </c>
+      <c r="F51">
+        <v>94</v>
+      </c>
+      <c r="G51">
+        <v>28</v>
+      </c>
+      <c r="H51">
+        <v>41</v>
+      </c>
+      <c r="I51">
+        <v>326</v>
+      </c>
+      <c r="J51">
+        <v>801</v>
+      </c>
+      <c r="K51">
+        <v>136</v>
+      </c>
+      <c r="L51">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52">
+        <v>230</v>
+      </c>
+      <c r="D52">
+        <v>27</v>
+      </c>
+      <c r="E52">
+        <v>118</v>
+      </c>
+      <c r="F52">
+        <v>98</v>
+      </c>
+      <c r="G52">
+        <v>44</v>
+      </c>
+      <c r="H52">
+        <v>75</v>
+      </c>
+      <c r="I52">
+        <v>619</v>
+      </c>
+      <c r="J52">
+        <v>1120</v>
+      </c>
+      <c r="K52">
+        <v>217</v>
+      </c>
+      <c r="L52">
+        <v>8.41</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" t="s">
+        <v>34</v>
+      </c>
+      <c r="C53">
+        <v>500</v>
+      </c>
+      <c r="D53">
+        <v>24</v>
+      </c>
+      <c r="E53">
+        <v>78</v>
+      </c>
+      <c r="F53">
+        <v>77</v>
+      </c>
+      <c r="G53">
+        <v>30</v>
+      </c>
+      <c r="H53">
+        <v>23</v>
+      </c>
+      <c r="I53">
+        <v>210</v>
+      </c>
+      <c r="J53">
+        <v>672</v>
+      </c>
+      <c r="K53">
+        <v>118</v>
+      </c>
+      <c r="L53">
+        <v>5.43</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" t="s">
+        <v>52</v>
+      </c>
+      <c r="C54">
+        <v>500</v>
+      </c>
+      <c r="D54">
+        <v>12</v>
+      </c>
+      <c r="E54">
+        <v>51</v>
+      </c>
+      <c r="F54">
+        <v>45</v>
+      </c>
+      <c r="G54">
+        <v>31</v>
+      </c>
+      <c r="H54">
+        <v>9</v>
+      </c>
+      <c r="I54">
+        <v>84</v>
+      </c>
+      <c r="J54">
+        <v>146</v>
+      </c>
+      <c r="K54">
+        <v>71</v>
+      </c>
+      <c r="L54">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55">
+        <v>115</v>
+      </c>
+      <c r="D55">
+        <v>11</v>
+      </c>
+      <c r="E55">
+        <v>94</v>
+      </c>
+      <c r="F55">
+        <v>82</v>
+      </c>
+      <c r="G55">
+        <v>29</v>
+      </c>
+      <c r="H55">
+        <v>40</v>
+      </c>
+      <c r="I55">
+        <v>300</v>
+      </c>
+      <c r="J55">
+        <v>926</v>
+      </c>
+      <c r="K55">
+        <v>179</v>
+      </c>
+      <c r="L55">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>42</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B56" t="s">
+        <v>29</v>
+      </c>
+      <c r="C56">
+        <v>230</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56">
+        <v>57</v>
+      </c>
+      <c r="F56">
+        <v>66</v>
+      </c>
+      <c r="G56">
+        <v>36</v>
+      </c>
+      <c r="H56">
+        <v>23</v>
+      </c>
+      <c r="I56">
+        <v>137</v>
+      </c>
+      <c r="J56">
+        <v>143</v>
+      </c>
+      <c r="K56">
+        <v>42</v>
+      </c>
+      <c r="L56">
+        <v>2.2400000000000002</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>16</v>
+      </c>
+      <c r="B57" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57">
+        <v>230</v>
+      </c>
+      <c r="D57">
+        <v>3</v>
+      </c>
+      <c r="E57">
+        <v>77</v>
+      </c>
+      <c r="F57">
+        <v>51</v>
+      </c>
+      <c r="G57">
+        <v>36</v>
+      </c>
+      <c r="H57">
+        <v>12</v>
+      </c>
+      <c r="I57">
+        <v>146</v>
+      </c>
+      <c r="J57">
+        <v>100</v>
+      </c>
+      <c r="K57">
+        <v>35</v>
+      </c>
+      <c r="L57">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>24</v>
+      </c>
+      <c r="B58" t="s">
+        <v>39</v>
+      </c>
+      <c r="C58">
+        <v>500</v>
+      </c>
+      <c r="D58">
+        <v>38</v>
+      </c>
+      <c r="E58">
+        <v>113</v>
+      </c>
+      <c r="F58">
+        <v>111</v>
+      </c>
+      <c r="G58">
+        <v>41</v>
+      </c>
+      <c r="H58">
+        <v>78</v>
+      </c>
+      <c r="I58">
+        <v>754</v>
+      </c>
+      <c r="J58">
+        <v>1456</v>
+      </c>
+      <c r="K58">
+        <v>259</v>
+      </c>
+      <c r="L58">
+        <v>10.32</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>21</v>
+      </c>
+      <c r="B59" t="s">
+        <v>53</v>
+      </c>
+      <c r="C59">
+        <v>500</v>
+      </c>
+      <c r="D59">
+        <v>32</v>
+      </c>
+      <c r="E59">
+        <v>112</v>
+      </c>
+      <c r="F59">
+        <v>97</v>
+      </c>
+      <c r="G59">
+        <v>40</v>
+      </c>
+      <c r="H59">
+        <v>86</v>
+      </c>
+      <c r="I59">
+        <v>601</v>
+      </c>
+      <c r="J59">
+        <v>1259</v>
+      </c>
+      <c r="K59">
+        <v>295</v>
+      </c>
+      <c r="L59">
+        <v>7.63</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>46</v>
+      </c>
+      <c r="B60" t="s">
+        <v>45</v>
+      </c>
+      <c r="C60">
+        <v>230</v>
+      </c>
+      <c r="D60">
+        <v>17</v>
+      </c>
+      <c r="E60">
+        <v>86</v>
+      </c>
+      <c r="F60">
+        <v>65</v>
+      </c>
+      <c r="G60">
+        <v>39</v>
+      </c>
+      <c r="H60">
+        <v>45</v>
+      </c>
+      <c r="I60">
+        <v>141</v>
+      </c>
+      <c r="J60">
+        <v>849</v>
+      </c>
+      <c r="K60">
+        <v>120</v>
+      </c>
+      <c r="L60">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>19</v>
+      </c>
+      <c r="B61" t="s">
+        <v>54</v>
+      </c>
+      <c r="C61">
+        <v>500</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61">
+        <v>63</v>
+      </c>
+      <c r="F61">
+        <v>58</v>
+      </c>
+      <c r="G61">
+        <v>39</v>
+      </c>
+      <c r="H61">
+        <v>9</v>
+      </c>
+      <c r="I61">
+        <v>114</v>
+      </c>
+      <c r="J61">
+        <v>247</v>
+      </c>
+      <c r="K61">
+        <v>19</v>
+      </c>
+      <c r="L61">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62">
+        <v>230</v>
+      </c>
+      <c r="D62">
+        <v>4</v>
+      </c>
+      <c r="E62">
+        <v>74</v>
+      </c>
+      <c r="F62">
+        <v>45</v>
+      </c>
+      <c r="G62">
+        <v>34</v>
+      </c>
+      <c r="H62">
+        <v>9</v>
+      </c>
+      <c r="I62">
+        <v>109</v>
+      </c>
+      <c r="J62">
+        <v>468</v>
+      </c>
+      <c r="K62">
+        <v>35</v>
+      </c>
+      <c r="L62">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" t="s">
+        <v>45</v>
+      </c>
+      <c r="C63">
+        <v>230</v>
+      </c>
+      <c r="D63">
+        <v>10</v>
+      </c>
+      <c r="E63">
+        <v>91</v>
+      </c>
+      <c r="F63">
+        <v>77</v>
+      </c>
+      <c r="G63">
+        <v>32</v>
+      </c>
+      <c r="H63">
+        <v>28</v>
+      </c>
+      <c r="I63">
+        <v>366</v>
+      </c>
+      <c r="J63">
+        <v>734</v>
+      </c>
+      <c r="K63">
+        <v>120</v>
+      </c>
+      <c r="L63">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64">
+        <v>500</v>
+      </c>
+      <c r="D64">
+        <v>5</v>
+      </c>
+      <c r="E64">
+        <v>42</v>
+      </c>
+      <c r="F64">
+        <v>73</v>
+      </c>
+      <c r="G64">
         <v>33</v>
       </c>
-      <c r="C50">
+      <c r="H64">
+        <v>18</v>
+      </c>
+      <c r="I64">
+        <v>32</v>
+      </c>
+      <c r="J64">
+        <v>225</v>
+      </c>
+      <c r="K64">
+        <v>34</v>
+      </c>
+      <c r="L64">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>14</v>
+      </c>
+      <c r="B65" t="s">
+        <v>17</v>
+      </c>
+      <c r="C65">
+        <v>500</v>
+      </c>
+      <c r="D65">
+        <v>19</v>
+      </c>
+      <c r="E65">
+        <v>86</v>
+      </c>
+      <c r="F65">
+        <v>67</v>
+      </c>
+      <c r="G65">
+        <v>30</v>
+      </c>
+      <c r="H65">
+        <v>47</v>
+      </c>
+      <c r="I65">
+        <v>299</v>
+      </c>
+      <c r="J65">
+        <v>402</v>
+      </c>
+      <c r="K65">
+        <v>64</v>
+      </c>
+      <c r="L65">
+        <v>5.55</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>19</v>
+      </c>
+      <c r="B66" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66">
+        <v>500</v>
+      </c>
+      <c r="D66">
+        <v>10</v>
+      </c>
+      <c r="E66">
+        <v>74</v>
+      </c>
+      <c r="F66">
+        <v>93</v>
+      </c>
+      <c r="G66">
+        <v>27</v>
+      </c>
+      <c r="H66">
+        <v>36</v>
+      </c>
+      <c r="I66">
+        <v>280</v>
+      </c>
+      <c r="J66">
+        <v>415</v>
+      </c>
+      <c r="K66">
+        <v>108</v>
+      </c>
+      <c r="L66">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>16</v>
+      </c>
+      <c r="B67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C67">
+        <v>500</v>
+      </c>
+      <c r="D67">
+        <v>9</v>
+      </c>
+      <c r="E67">
+        <v>60</v>
+      </c>
+      <c r="F67">
+        <v>47</v>
+      </c>
+      <c r="G67">
+        <v>32</v>
+      </c>
+      <c r="H67">
+        <v>16</v>
+      </c>
+      <c r="I67">
+        <v>92</v>
+      </c>
+      <c r="J67">
+        <v>243</v>
+      </c>
+      <c r="K67">
+        <v>21</v>
+      </c>
+      <c r="L67">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68" t="s">
+        <v>55</v>
+      </c>
+      <c r="C68">
+        <v>500</v>
+      </c>
+      <c r="D68">
+        <v>36</v>
+      </c>
+      <c r="E68">
+        <v>98</v>
+      </c>
+      <c r="F68">
+        <v>104</v>
+      </c>
+      <c r="G68">
+        <v>30</v>
+      </c>
+      <c r="H68">
+        <v>86</v>
+      </c>
+      <c r="I68">
+        <v>911</v>
+      </c>
+      <c r="J68">
+        <v>1141</v>
+      </c>
+      <c r="K68">
+        <v>485</v>
+      </c>
+      <c r="L68">
+        <v>11.98</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>12</v>
+      </c>
+      <c r="B69" t="s">
+        <v>50</v>
+      </c>
+      <c r="C69">
         <v>230</v>
       </c>
-      <c r="D50">
+      <c r="D69">
+        <v>25</v>
+      </c>
+      <c r="E69">
+        <v>90</v>
+      </c>
+      <c r="F69">
+        <v>93</v>
+      </c>
+      <c r="G69">
+        <v>40</v>
+      </c>
+      <c r="H69">
+        <v>81</v>
+      </c>
+      <c r="I69">
+        <v>999</v>
+      </c>
+      <c r="J69">
+        <v>1583</v>
+      </c>
+      <c r="K69">
+        <v>169</v>
+      </c>
+      <c r="L69">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>14</v>
+      </c>
+      <c r="B70" t="s">
+        <v>56</v>
+      </c>
+      <c r="C70">
+        <v>500</v>
+      </c>
+      <c r="D70">
+        <v>20</v>
+      </c>
+      <c r="E70">
+        <v>101</v>
+      </c>
+      <c r="F70">
+        <v>115</v>
+      </c>
+      <c r="G70">
+        <v>31</v>
+      </c>
+      <c r="H70">
+        <v>81</v>
+      </c>
+      <c r="I70">
+        <v>740</v>
+      </c>
+      <c r="J70">
+        <v>1429</v>
+      </c>
+      <c r="K70">
+        <v>174</v>
+      </c>
+      <c r="L70">
+        <v>10.61</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>26</v>
+      </c>
+      <c r="B71" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71">
+        <v>500</v>
+      </c>
+      <c r="D71">
+        <v>39</v>
+      </c>
+      <c r="E71">
+        <v>116</v>
+      </c>
+      <c r="F71">
+        <v>88</v>
+      </c>
+      <c r="G71">
+        <v>36</v>
+      </c>
+      <c r="H71">
+        <v>93</v>
+      </c>
+      <c r="I71">
+        <v>853</v>
+      </c>
+      <c r="J71">
+        <v>1548</v>
+      </c>
+      <c r="K71">
+        <v>403</v>
+      </c>
+      <c r="L71">
+        <v>11.69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>12</v>
+      </c>
+      <c r="B72" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72">
+        <v>115</v>
+      </c>
+      <c r="D72">
+        <v>2</v>
+      </c>
+      <c r="E72">
+        <v>48</v>
+      </c>
+      <c r="F72">
+        <v>72</v>
+      </c>
+      <c r="G72">
+        <v>31</v>
+      </c>
+      <c r="H72">
         <v>18</v>
       </c>
-      <c r="E50">
+      <c r="I72">
+        <v>46</v>
+      </c>
+      <c r="J72">
+        <v>272</v>
+      </c>
+      <c r="K72">
+        <v>44</v>
+      </c>
+      <c r="L72">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>48</v>
+      </c>
+      <c r="B73" t="s">
+        <v>59</v>
+      </c>
+      <c r="C73">
+        <v>230</v>
+      </c>
+      <c r="D73">
+        <v>6</v>
+      </c>
+      <c r="E73">
+        <v>46</v>
+      </c>
+      <c r="F73">
+        <v>46</v>
+      </c>
+      <c r="G73">
+        <v>28</v>
+      </c>
+      <c r="H73">
+        <v>5</v>
+      </c>
+      <c r="I73">
+        <v>118</v>
+      </c>
+      <c r="J73">
+        <v>263</v>
+      </c>
+      <c r="K73">
+        <v>10</v>
+      </c>
+      <c r="L73">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>46</v>
+      </c>
+      <c r="B74" t="s">
+        <v>60</v>
+      </c>
+      <c r="C74">
+        <v>230</v>
+      </c>
+      <c r="D74">
+        <v>7</v>
+      </c>
+      <c r="E74">
+        <v>59</v>
+      </c>
+      <c r="F74">
+        <v>67</v>
+      </c>
+      <c r="G74">
+        <v>28</v>
+      </c>
+      <c r="H74">
+        <v>14</v>
+      </c>
+      <c r="I74">
+        <v>28</v>
+      </c>
+      <c r="J74">
+        <v>290</v>
+      </c>
+      <c r="K74">
+        <v>20</v>
+      </c>
+      <c r="L74">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>42</v>
+      </c>
+      <c r="B75" t="s">
+        <v>61</v>
+      </c>
+      <c r="C75">
+        <v>230</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75">
+        <v>41</v>
+      </c>
+      <c r="F75">
+        <v>74</v>
+      </c>
+      <c r="G75">
+        <v>27</v>
+      </c>
+      <c r="H75">
+        <v>9</v>
+      </c>
+      <c r="I75">
+        <v>30</v>
+      </c>
+      <c r="J75">
+        <v>190</v>
+      </c>
+      <c r="K75">
+        <v>72</v>
+      </c>
+      <c r="L75">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>14</v>
+      </c>
+      <c r="B76" t="s">
+        <v>62</v>
+      </c>
+      <c r="C76">
+        <v>500</v>
+      </c>
+      <c r="D76">
+        <v>35</v>
+      </c>
+      <c r="E76">
+        <v>114</v>
+      </c>
+      <c r="F76">
+        <v>105</v>
+      </c>
+      <c r="G76">
+        <v>34</v>
+      </c>
+      <c r="H76">
+        <v>76</v>
+      </c>
+      <c r="I76">
+        <v>529</v>
+      </c>
+      <c r="J76">
+        <v>1477</v>
+      </c>
+      <c r="K76">
+        <v>412</v>
+      </c>
+      <c r="L76">
+        <v>8.59</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>21</v>
+      </c>
+      <c r="B77" t="s">
+        <v>51</v>
+      </c>
+      <c r="C77">
+        <v>115</v>
+      </c>
+      <c r="D77">
+        <v>13</v>
+      </c>
+      <c r="E77">
+        <v>42</v>
+      </c>
+      <c r="F77">
+        <v>70</v>
+      </c>
+      <c r="G77">
+        <v>38</v>
+      </c>
+      <c r="H77">
+        <v>5</v>
+      </c>
+      <c r="I77">
+        <v>51</v>
+      </c>
+      <c r="J77">
+        <v>326</v>
+      </c>
+      <c r="K77">
+        <v>60</v>
+      </c>
+      <c r="L77">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>48</v>
+      </c>
+      <c r="B78" t="s">
+        <v>35</v>
+      </c>
+      <c r="C78">
+        <v>500</v>
+      </c>
+      <c r="D78">
+        <v>17</v>
+      </c>
+      <c r="E78">
+        <v>76</v>
+      </c>
+      <c r="F78">
+        <v>78</v>
+      </c>
+      <c r="G78">
+        <v>31</v>
+      </c>
+      <c r="H78">
+        <v>25</v>
+      </c>
+      <c r="I78">
+        <v>111</v>
+      </c>
+      <c r="J78">
+        <v>438</v>
+      </c>
+      <c r="K78">
+        <v>132</v>
+      </c>
+      <c r="L78">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>40</v>
+      </c>
+      <c r="B79" t="s">
+        <v>39</v>
+      </c>
+      <c r="C79">
+        <v>500</v>
+      </c>
+      <c r="D79">
+        <v>35</v>
+      </c>
+      <c r="E79">
+        <v>107</v>
+      </c>
+      <c r="F79">
+        <v>110</v>
+      </c>
+      <c r="G79">
+        <v>33</v>
+      </c>
+      <c r="H79">
+        <v>43</v>
+      </c>
+      <c r="I79">
+        <v>896</v>
+      </c>
+      <c r="J79">
+        <v>948</v>
+      </c>
+      <c r="K79">
+        <v>161</v>
+      </c>
+      <c r="L79">
+        <v>8.84</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>43</v>
+      </c>
+      <c r="B80" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80">
+        <v>500</v>
+      </c>
+      <c r="D80">
+        <v>7</v>
+      </c>
+      <c r="E80">
+        <v>69</v>
+      </c>
+      <c r="F80">
+        <v>47</v>
+      </c>
+      <c r="G80">
+        <v>25</v>
+      </c>
+      <c r="H80">
+        <v>12</v>
+      </c>
+      <c r="I80">
+        <v>144</v>
+      </c>
+      <c r="J80">
+        <v>351</v>
+      </c>
+      <c r="K80">
+        <v>59</v>
+      </c>
+      <c r="L80">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>26</v>
+      </c>
+      <c r="B81" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81">
+        <v>500</v>
+      </c>
+      <c r="D81">
+        <v>28</v>
+      </c>
+      <c r="E81">
         <v>89</v>
       </c>
-      <c r="F50">
+      <c r="F81">
+        <v>91</v>
+      </c>
+      <c r="G81">
+        <v>25</v>
+      </c>
+      <c r="H81">
+        <v>33</v>
+      </c>
+      <c r="I81">
+        <v>367</v>
+      </c>
+      <c r="J81">
+        <v>775</v>
+      </c>
+      <c r="K81">
+        <v>97</v>
+      </c>
+      <c r="L81">
+        <v>5.12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>24</v>
+      </c>
+      <c r="B82" t="s">
+        <v>22</v>
+      </c>
+      <c r="C82">
+        <v>230</v>
+      </c>
+      <c r="D82">
+        <v>6</v>
+      </c>
+      <c r="E82">
+        <v>57</v>
+      </c>
+      <c r="F82">
+        <v>70</v>
+      </c>
+      <c r="G82">
+        <v>29</v>
+      </c>
+      <c r="H82">
+        <v>5</v>
+      </c>
+      <c r="I82">
+        <v>61</v>
+      </c>
+      <c r="J82">
+        <v>272</v>
+      </c>
+      <c r="K82">
+        <v>10</v>
+      </c>
+      <c r="L82">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>19</v>
+      </c>
+      <c r="B83" t="s">
+        <v>32</v>
+      </c>
+      <c r="C83">
+        <v>230</v>
+      </c>
+      <c r="D83">
+        <v>4</v>
+      </c>
+      <c r="E83">
+        <v>73</v>
+      </c>
+      <c r="F83">
+        <v>70</v>
+      </c>
+      <c r="G83">
+        <v>25</v>
+      </c>
+      <c r="H83">
+        <v>17</v>
+      </c>
+      <c r="I83">
+        <v>38</v>
+      </c>
+      <c r="J83">
+        <v>358</v>
+      </c>
+      <c r="K83">
+        <v>59</v>
+      </c>
+      <c r="L83">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>33</v>
+      </c>
+      <c r="B84" t="s">
+        <v>44</v>
+      </c>
+      <c r="C84">
+        <v>500</v>
+      </c>
+      <c r="D84">
+        <v>28</v>
+      </c>
+      <c r="E84">
+        <v>92</v>
+      </c>
+      <c r="F84">
+        <v>115</v>
+      </c>
+      <c r="G84">
+        <v>42</v>
+      </c>
+      <c r="H84">
+        <v>98</v>
+      </c>
+      <c r="I84">
+        <v>830</v>
+      </c>
+      <c r="J84">
+        <v>1537</v>
+      </c>
+      <c r="K84">
+        <v>465</v>
+      </c>
+      <c r="L84">
+        <v>7.76</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>37</v>
+      </c>
+      <c r="B85" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85">
+        <v>500</v>
+      </c>
+      <c r="D85">
+        <v>30</v>
+      </c>
+      <c r="E85">
+        <v>91</v>
+      </c>
+      <c r="F85">
+        <v>85</v>
+      </c>
+      <c r="G85">
+        <v>31</v>
+      </c>
+      <c r="H85">
+        <v>55</v>
+      </c>
+      <c r="I85">
+        <v>727</v>
+      </c>
+      <c r="J85">
+        <v>1289</v>
+      </c>
+      <c r="K85">
+        <v>298</v>
+      </c>
+      <c r="L85">
+        <v>5.47</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>40</v>
+      </c>
+      <c r="B86" t="s">
+        <v>28</v>
+      </c>
+      <c r="C86">
+        <v>230</v>
+      </c>
+      <c r="D86">
+        <v>32</v>
+      </c>
+      <c r="E86">
+        <v>100</v>
+      </c>
+      <c r="F86">
+        <v>105</v>
+      </c>
+      <c r="G86">
+        <v>35</v>
+      </c>
+      <c r="H86">
+        <v>47</v>
+      </c>
+      <c r="I86">
+        <v>941</v>
+      </c>
+      <c r="J86">
+        <v>1924</v>
+      </c>
+      <c r="K86">
+        <v>232</v>
+      </c>
+      <c r="L86">
+        <v>9.4600000000000009</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>19</v>
+      </c>
+      <c r="B87" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87">
+        <v>115</v>
+      </c>
+      <c r="D87">
+        <v>22</v>
+      </c>
+      <c r="E87">
+        <v>107</v>
+      </c>
+      <c r="F87">
+        <v>91</v>
+      </c>
+      <c r="G87">
+        <v>42</v>
+      </c>
+      <c r="H87">
+        <v>65</v>
+      </c>
+      <c r="I87">
+        <v>459</v>
+      </c>
+      <c r="J87">
+        <v>1360</v>
+      </c>
+      <c r="K87">
+        <v>305</v>
+      </c>
+      <c r="L87">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>12</v>
+      </c>
+      <c r="B88" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88">
+        <v>230</v>
+      </c>
+      <c r="D88">
+        <v>34</v>
+      </c>
+      <c r="E88">
+        <v>95</v>
+      </c>
+      <c r="F88">
+        <v>95</v>
+      </c>
+      <c r="G88">
+        <v>34</v>
+      </c>
+      <c r="H88">
+        <v>52</v>
+      </c>
+      <c r="I88">
+        <v>879</v>
+      </c>
+      <c r="J88">
+        <v>1308</v>
+      </c>
+      <c r="K88">
+        <v>309</v>
+      </c>
+      <c r="L88">
+        <v>8.2200000000000006</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>24</v>
+      </c>
+      <c r="B89" t="s">
+        <v>59</v>
+      </c>
+      <c r="C89">
+        <v>230</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>50</v>
+      </c>
+      <c r="F89">
+        <v>72</v>
+      </c>
+      <c r="G89">
+        <v>31</v>
+      </c>
+      <c r="H89">
+        <v>5</v>
+      </c>
+      <c r="I89">
+        <v>17</v>
+      </c>
+      <c r="J89">
+        <v>316</v>
+      </c>
+      <c r="K89">
+        <v>17</v>
+      </c>
+      <c r="L89">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>40</v>
+      </c>
+      <c r="B90" t="s">
+        <v>55</v>
+      </c>
+      <c r="C90">
+        <v>500</v>
+      </c>
+      <c r="D90">
+        <v>7</v>
+      </c>
+      <c r="E90">
+        <v>66</v>
+      </c>
+      <c r="F90">
+        <v>67</v>
+      </c>
+      <c r="G90">
+        <v>27</v>
+      </c>
+      <c r="H90">
+        <v>16</v>
+      </c>
+      <c r="I90">
+        <v>14</v>
+      </c>
+      <c r="J90">
+        <v>473</v>
+      </c>
+      <c r="K90">
+        <v>12</v>
+      </c>
+      <c r="L90">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>40</v>
+      </c>
+      <c r="B91" t="s">
+        <v>28</v>
+      </c>
+      <c r="C91">
+        <v>230</v>
+      </c>
+      <c r="D91">
+        <v>26</v>
+      </c>
+      <c r="E91">
+        <v>76</v>
+      </c>
+      <c r="F91">
+        <v>88</v>
+      </c>
+      <c r="G91">
+        <v>36</v>
+      </c>
+      <c r="H91">
+        <v>49</v>
+      </c>
+      <c r="I91">
+        <v>124</v>
+      </c>
+      <c r="J91">
+        <v>828</v>
+      </c>
+      <c r="K91">
+        <v>198</v>
+      </c>
+      <c r="L91">
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>40</v>
+      </c>
+      <c r="B92" t="s">
+        <v>63</v>
+      </c>
+      <c r="C92">
+        <v>115</v>
+      </c>
+      <c r="D92">
+        <v>21</v>
+      </c>
+      <c r="E92">
+        <v>94</v>
+      </c>
+      <c r="F92">
+        <v>103</v>
+      </c>
+      <c r="G92">
+        <v>44</v>
+      </c>
+      <c r="H92">
+        <v>60</v>
+      </c>
+      <c r="I92">
+        <v>587</v>
+      </c>
+      <c r="J92">
+        <v>1160</v>
+      </c>
+      <c r="K92">
+        <v>279</v>
+      </c>
+      <c r="L92">
+        <v>10.51</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>43</v>
+      </c>
+      <c r="B93" t="s">
+        <v>17</v>
+      </c>
+      <c r="C93">
+        <v>500</v>
+      </c>
+      <c r="D93">
+        <v>4</v>
+      </c>
+      <c r="E93">
+        <v>57</v>
+      </c>
+      <c r="F93">
+        <v>59</v>
+      </c>
+      <c r="G93">
+        <v>37</v>
+      </c>
+      <c r="H93">
+        <v>9</v>
+      </c>
+      <c r="I93">
+        <v>44</v>
+      </c>
+      <c r="J93">
+        <v>441</v>
+      </c>
+      <c r="K93">
+        <v>25</v>
+      </c>
+      <c r="L93">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>26</v>
+      </c>
+      <c r="B94" t="s">
+        <v>36</v>
+      </c>
+      <c r="C94">
+        <v>500</v>
+      </c>
+      <c r="D94">
+        <v>29</v>
+      </c>
+      <c r="E94">
+        <v>90</v>
+      </c>
+      <c r="F94">
+        <v>72</v>
+      </c>
+      <c r="G94">
+        <v>27</v>
+      </c>
+      <c r="H94">
+        <v>37</v>
+      </c>
+      <c r="I94">
+        <v>391</v>
+      </c>
+      <c r="J94">
+        <v>800</v>
+      </c>
+      <c r="K94">
+        <v>180</v>
+      </c>
+      <c r="L94">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>33</v>
+      </c>
+      <c r="B95" t="s">
+        <v>56</v>
+      </c>
+      <c r="C95">
+        <v>500</v>
+      </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
+      <c r="E95">
+        <v>51</v>
+      </c>
+      <c r="F95">
+        <v>58</v>
+      </c>
+      <c r="G95">
+        <v>39</v>
+      </c>
+      <c r="H95">
+        <v>16</v>
+      </c>
+      <c r="I95">
+        <v>110</v>
+      </c>
+      <c r="J95">
+        <v>445</v>
+      </c>
+      <c r="K95">
+        <v>42</v>
+      </c>
+      <c r="L95">
+        <v>2.3199999999999998</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>24</v>
+      </c>
+      <c r="B96" t="s">
+        <v>23</v>
+      </c>
+      <c r="C96">
+        <v>500</v>
+      </c>
+      <c r="D96">
+        <v>23</v>
+      </c>
+      <c r="E96">
+        <v>116</v>
+      </c>
+      <c r="F96">
+        <v>109</v>
+      </c>
+      <c r="G96">
+        <v>42</v>
+      </c>
+      <c r="H96">
+        <v>81</v>
+      </c>
+      <c r="I96">
+        <v>860</v>
+      </c>
+      <c r="J96">
+        <v>1141</v>
+      </c>
+      <c r="K96">
+        <v>205</v>
+      </c>
+      <c r="L96">
+        <v>11.27</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>24</v>
+      </c>
+      <c r="B97" t="s">
+        <v>49</v>
+      </c>
+      <c r="C97">
+        <v>500</v>
+      </c>
+      <c r="D97">
+        <v>25</v>
+      </c>
+      <c r="E97">
+        <v>106</v>
+      </c>
+      <c r="F97">
+        <v>118</v>
+      </c>
+      <c r="G97">
+        <v>41</v>
+      </c>
+      <c r="H97">
+        <v>67</v>
+      </c>
+      <c r="I97">
+        <v>920</v>
+      </c>
+      <c r="J97">
+        <v>1569</v>
+      </c>
+      <c r="K97">
+        <v>300</v>
+      </c>
+      <c r="L97">
+        <v>9.82</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>40</v>
+      </c>
+      <c r="B98" t="s">
+        <v>47</v>
+      </c>
+      <c r="C98">
+        <v>115</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98">
+        <v>59</v>
+      </c>
+      <c r="F98">
+        <v>61</v>
+      </c>
+      <c r="G98">
+        <v>34</v>
+      </c>
+      <c r="H98">
+        <v>24</v>
+      </c>
+      <c r="I98">
+        <v>108</v>
+      </c>
+      <c r="J98">
+        <v>157</v>
+      </c>
+      <c r="K98">
+        <v>75</v>
+      </c>
+      <c r="L98">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>46</v>
+      </c>
+      <c r="B99" t="s">
+        <v>36</v>
+      </c>
+      <c r="C99">
+        <v>230</v>
+      </c>
+      <c r="D99">
+        <v>18</v>
+      </c>
+      <c r="E99">
+        <v>89</v>
+      </c>
+      <c r="F99">
         <v>86</v>
       </c>
-      <c r="G50">
+      <c r="G99">
         <v>32</v>
       </c>
-      <c r="H50">
+      <c r="H99">
         <v>41</v>
       </c>
-      <c r="I50">
+      <c r="I99">
         <v>125</v>
       </c>
-      <c r="J50">
+      <c r="J99">
         <v>692</v>
       </c>
-      <c r="K50">
+      <c r="K99">
         <v>149</v>
       </c>
-      <c r="L50">
+      <c r="L99">
         <v>2.59</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>33</v>
+      </c>
+      <c r="B100" t="s">
+        <v>56</v>
+      </c>
+      <c r="C100">
+        <v>500</v>
+      </c>
+      <c r="D100">
+        <v>5</v>
+      </c>
+      <c r="E100">
+        <v>47</v>
+      </c>
+      <c r="F100">
+        <v>45</v>
+      </c>
+      <c r="G100">
+        <v>34</v>
+      </c>
+      <c r="H100">
+        <v>11</v>
+      </c>
+      <c r="I100">
+        <v>71</v>
+      </c>
+      <c r="J100">
+        <v>100</v>
+      </c>
+      <c r="K100">
+        <v>42</v>
+      </c>
+      <c r="L100">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>24</v>
+      </c>
+      <c r="B101" t="s">
+        <v>28</v>
+      </c>
+      <c r="C101">
+        <v>115</v>
+      </c>
+      <c r="D101">
+        <v>21</v>
+      </c>
+      <c r="E101">
+        <v>86</v>
+      </c>
+      <c r="F101">
+        <v>92</v>
+      </c>
+      <c r="G101">
+        <v>38</v>
+      </c>
+      <c r="H101">
+        <v>44</v>
+      </c>
+      <c r="I101">
+        <v>111</v>
+      </c>
+      <c r="J101">
+        <v>839</v>
+      </c>
+      <c r="K101">
+        <v>126</v>
+      </c>
+      <c r="L101">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>26</v>
+      </c>
+      <c r="B102" t="s">
+        <v>60</v>
+      </c>
+      <c r="C102">
+        <v>115</v>
+      </c>
+      <c r="D102">
+        <v>23</v>
+      </c>
+      <c r="E102">
+        <v>109</v>
+      </c>
+      <c r="F102">
+        <v>92</v>
+      </c>
+      <c r="G102">
+        <v>41</v>
+      </c>
+      <c r="H102">
+        <v>47</v>
+      </c>
+      <c r="I102">
+        <v>501</v>
+      </c>
+      <c r="J102">
+        <v>1995</v>
+      </c>
+      <c r="K102">
+        <v>222</v>
+      </c>
+      <c r="L102">
+        <v>7.14</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>37</v>
+      </c>
+      <c r="B103" t="s">
+        <v>49</v>
+      </c>
+      <c r="C103">
+        <v>115</v>
+      </c>
+      <c r="D103">
+        <v>2</v>
+      </c>
+      <c r="E103">
+        <v>71</v>
+      </c>
+      <c r="F103">
+        <v>47</v>
+      </c>
+      <c r="G103">
+        <v>26</v>
+      </c>
+      <c r="H103">
+        <v>9</v>
+      </c>
+      <c r="I103">
+        <v>105</v>
+      </c>
+      <c r="J103">
+        <v>225</v>
+      </c>
+      <c r="K103">
+        <v>55</v>
+      </c>
+      <c r="L103">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>48</v>
+      </c>
+      <c r="B104" t="s">
+        <v>34</v>
+      </c>
+      <c r="C104">
+        <v>115</v>
+      </c>
+      <c r="D104">
+        <v>3</v>
+      </c>
+      <c r="E104">
+        <v>47</v>
+      </c>
+      <c r="F104">
+        <v>73</v>
+      </c>
+      <c r="G104">
+        <v>34</v>
+      </c>
+      <c r="H104">
+        <v>14</v>
+      </c>
+      <c r="I104">
+        <v>36</v>
+      </c>
+      <c r="J104">
+        <v>472</v>
+      </c>
+      <c r="K104">
+        <v>43</v>
+      </c>
+      <c r="L104">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>41</v>
+      </c>
+      <c r="B105" t="s">
+        <v>57</v>
+      </c>
+      <c r="C105">
+        <v>115</v>
+      </c>
+      <c r="D105">
+        <v>14</v>
+      </c>
+      <c r="E105">
+        <v>40</v>
+      </c>
+      <c r="F105">
+        <v>49</v>
+      </c>
+      <c r="G105">
+        <v>34</v>
+      </c>
+      <c r="H105">
+        <v>16</v>
+      </c>
+      <c r="I105">
+        <v>99</v>
+      </c>
+      <c r="J105">
+        <v>426</v>
+      </c>
+      <c r="K105">
+        <v>37</v>
+      </c>
+      <c r="L105">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>33</v>
+      </c>
+      <c r="B106" t="s">
+        <v>53</v>
+      </c>
+      <c r="C106">
+        <v>115</v>
+      </c>
+      <c r="D106">
+        <v>4</v>
+      </c>
+      <c r="E106">
+        <v>72</v>
+      </c>
+      <c r="F106">
+        <v>52</v>
+      </c>
+      <c r="G106">
+        <v>27</v>
+      </c>
+      <c r="H106">
+        <v>15</v>
+      </c>
+      <c r="I106">
+        <v>142</v>
+      </c>
+      <c r="J106">
+        <v>119</v>
+      </c>
+      <c r="K106">
+        <v>13</v>
+      </c>
+      <c r="L106">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>12</v>
+      </c>
+      <c r="B107" t="s">
+        <v>61</v>
+      </c>
+      <c r="C107">
+        <v>500</v>
+      </c>
+      <c r="D107">
+        <v>22</v>
+      </c>
+      <c r="E107">
+        <v>89</v>
+      </c>
+      <c r="F107">
+        <v>79</v>
+      </c>
+      <c r="G107">
+        <v>31</v>
+      </c>
+      <c r="H107">
+        <v>37</v>
+      </c>
+      <c r="I107">
+        <v>343</v>
+      </c>
+      <c r="J107">
+        <v>438</v>
+      </c>
+      <c r="K107">
+        <v>62</v>
+      </c>
+      <c r="L107">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>43</v>
+      </c>
+      <c r="B108" t="s">
+        <v>36</v>
+      </c>
+      <c r="C108">
+        <v>115</v>
+      </c>
+      <c r="D108">
+        <v>10</v>
+      </c>
+      <c r="E108">
+        <v>77</v>
+      </c>
+      <c r="F108">
+        <v>60</v>
+      </c>
+      <c r="G108">
+        <v>26</v>
+      </c>
+      <c r="H108">
+        <v>5</v>
+      </c>
+      <c r="I108">
+        <v>16</v>
+      </c>
+      <c r="J108">
+        <v>242</v>
+      </c>
+      <c r="K108">
+        <v>48</v>
+      </c>
+      <c r="L108">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>21</v>
+      </c>
+      <c r="B109" t="s">
+        <v>27</v>
+      </c>
+      <c r="C109">
+        <v>230</v>
+      </c>
+      <c r="D109">
+        <v>11</v>
+      </c>
+      <c r="E109">
+        <v>74</v>
+      </c>
+      <c r="F109">
+        <v>62</v>
+      </c>
+      <c r="G109">
+        <v>39</v>
+      </c>
+      <c r="H109">
+        <v>6</v>
+      </c>
+      <c r="I109">
+        <v>85</v>
+      </c>
+      <c r="J109">
+        <v>216</v>
+      </c>
+      <c r="K109">
+        <v>68</v>
+      </c>
+      <c r="L109">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>37</v>
+      </c>
+      <c r="B110" t="s">
+        <v>52</v>
+      </c>
+      <c r="C110">
+        <v>500</v>
+      </c>
+      <c r="D110">
+        <v>31</v>
+      </c>
+      <c r="E110">
+        <v>104</v>
+      </c>
+      <c r="F110">
+        <v>109</v>
+      </c>
+      <c r="G110">
+        <v>40</v>
+      </c>
+      <c r="H110">
+        <v>63</v>
+      </c>
+      <c r="I110">
+        <v>680</v>
+      </c>
+      <c r="J110">
+        <v>933</v>
+      </c>
+      <c r="K110">
+        <v>246</v>
+      </c>
+      <c r="L110">
+        <v>5.59</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>33</v>
+      </c>
+      <c r="B111" t="s">
+        <v>13</v>
+      </c>
+      <c r="C111">
+        <v>115</v>
+      </c>
+      <c r="D111">
+        <v>29</v>
+      </c>
+      <c r="E111">
+        <v>113</v>
+      </c>
+      <c r="F111">
+        <v>113</v>
+      </c>
+      <c r="G111">
+        <v>43</v>
+      </c>
+      <c r="H111">
+        <v>89</v>
+      </c>
+      <c r="I111">
+        <v>366</v>
+      </c>
+      <c r="J111">
+        <v>1981</v>
+      </c>
+      <c r="K111">
+        <v>401</v>
+      </c>
+      <c r="L111">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>16</v>
+      </c>
+      <c r="B112" t="s">
+        <v>45</v>
+      </c>
+      <c r="C112">
+        <v>500</v>
+      </c>
+      <c r="D112">
+        <v>14</v>
+      </c>
+      <c r="E112">
+        <v>92</v>
+      </c>
+      <c r="F112">
+        <v>94</v>
+      </c>
+      <c r="G112">
+        <v>26</v>
+      </c>
+      <c r="H112">
+        <v>27</v>
+      </c>
+      <c r="I112">
+        <v>395</v>
+      </c>
+      <c r="J112">
+        <v>918</v>
+      </c>
+      <c r="K112">
+        <v>183</v>
+      </c>
+      <c r="L112">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>40</v>
+      </c>
+      <c r="B113" t="s">
+        <v>39</v>
+      </c>
+      <c r="C113">
+        <v>230</v>
+      </c>
+      <c r="D113">
+        <v>4</v>
+      </c>
+      <c r="E113">
+        <v>55</v>
+      </c>
+      <c r="F113">
+        <v>58</v>
+      </c>
+      <c r="G113">
+        <v>29</v>
+      </c>
+      <c r="H113">
+        <v>8</v>
+      </c>
+      <c r="I113">
+        <v>126</v>
+      </c>
+      <c r="J113">
+        <v>416</v>
+      </c>
+      <c r="K113">
+        <v>15</v>
+      </c>
+      <c r="L113">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>19</v>
+      </c>
+      <c r="B114" t="s">
+        <v>36</v>
+      </c>
+      <c r="C114">
+        <v>500</v>
+      </c>
+      <c r="D114">
+        <v>13</v>
+      </c>
+      <c r="E114">
+        <v>90</v>
+      </c>
+      <c r="F114">
+        <v>93</v>
+      </c>
+      <c r="G114">
+        <v>29</v>
+      </c>
+      <c r="H114">
+        <v>45</v>
+      </c>
+      <c r="I114">
+        <v>251</v>
+      </c>
+      <c r="J114">
+        <v>925</v>
+      </c>
+      <c r="K114">
+        <v>131</v>
+      </c>
+      <c r="L114">
+        <v>4.9400000000000004</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>16</v>
+      </c>
+      <c r="B115" t="s">
+        <v>13</v>
+      </c>
+      <c r="C115">
+        <v>500</v>
+      </c>
+      <c r="D115">
+        <v>7</v>
+      </c>
+      <c r="E115">
+        <v>55</v>
+      </c>
+      <c r="F115">
+        <v>68</v>
+      </c>
+      <c r="G115">
+        <v>27</v>
+      </c>
+      <c r="H115">
+        <v>21</v>
+      </c>
+      <c r="I115">
+        <v>22</v>
+      </c>
+      <c r="J115">
+        <v>319</v>
+      </c>
+      <c r="K115">
+        <v>56</v>
+      </c>
+      <c r="L115">
+        <v>2.4900000000000002</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>48</v>
+      </c>
+      <c r="B116" t="s">
+        <v>53</v>
+      </c>
+      <c r="C116">
+        <v>230</v>
+      </c>
+      <c r="D116">
+        <v>21</v>
+      </c>
+      <c r="E116">
+        <v>93</v>
+      </c>
+      <c r="F116">
+        <v>74</v>
+      </c>
+      <c r="G116">
+        <v>27</v>
+      </c>
+      <c r="H116">
+        <v>46</v>
+      </c>
+      <c r="I116">
+        <v>271</v>
+      </c>
+      <c r="J116">
+        <v>673</v>
+      </c>
+      <c r="K116">
+        <v>184</v>
+      </c>
+      <c r="L116">
+        <v>4.3899999999999997</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>41</v>
+      </c>
+      <c r="B117" t="s">
+        <v>39</v>
+      </c>
+      <c r="C117">
+        <v>115</v>
+      </c>
+      <c r="D117">
+        <v>17</v>
+      </c>
+      <c r="E117">
+        <v>93</v>
+      </c>
+      <c r="F117">
+        <v>87</v>
+      </c>
+      <c r="G117">
+        <v>29</v>
+      </c>
+      <c r="H117">
+        <v>31</v>
+      </c>
+      <c r="I117">
+        <v>116</v>
+      </c>
+      <c r="J117">
+        <v>644</v>
+      </c>
+      <c r="K117">
+        <v>70</v>
+      </c>
+      <c r="L117">
+        <v>5.78</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>41</v>
+      </c>
+      <c r="B118" t="s">
+        <v>25</v>
+      </c>
+      <c r="C118">
+        <v>230</v>
+      </c>
+      <c r="D118">
+        <v>23</v>
+      </c>
+      <c r="E118">
+        <v>94</v>
+      </c>
+      <c r="F118">
+        <v>102</v>
+      </c>
+      <c r="G118">
+        <v>34</v>
+      </c>
+      <c r="H118">
+        <v>50</v>
+      </c>
+      <c r="I118">
+        <v>960</v>
+      </c>
+      <c r="J118">
+        <v>1469</v>
+      </c>
+      <c r="K118">
+        <v>438</v>
+      </c>
+      <c r="L118">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>12</v>
+      </c>
+      <c r="B119" t="s">
+        <v>31</v>
+      </c>
+      <c r="C119">
+        <v>115</v>
+      </c>
+      <c r="D119">
+        <v>9</v>
+      </c>
+      <c r="E119">
+        <v>60</v>
+      </c>
+      <c r="F119">
+        <v>46</v>
+      </c>
+      <c r="G119">
+        <v>28</v>
+      </c>
+      <c r="H119">
+        <v>16</v>
+      </c>
+      <c r="I119">
+        <v>62</v>
+      </c>
+      <c r="J119">
+        <v>302</v>
+      </c>
+      <c r="K119">
+        <v>62</v>
+      </c>
+      <c r="L119">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>46</v>
+      </c>
+      <c r="B120" t="s">
+        <v>34</v>
+      </c>
+      <c r="C120">
+        <v>500</v>
+      </c>
+      <c r="D120">
+        <v>3</v>
+      </c>
+      <c r="E120">
+        <v>72</v>
+      </c>
+      <c r="F120">
+        <v>65</v>
+      </c>
+      <c r="G120">
+        <v>38</v>
+      </c>
+      <c r="H120">
+        <v>16</v>
+      </c>
+      <c r="I120">
+        <v>39</v>
+      </c>
+      <c r="J120">
+        <v>416</v>
+      </c>
+      <c r="K120">
+        <v>65</v>
+      </c>
+      <c r="L120">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>43</v>
+      </c>
+      <c r="B121" t="s">
+        <v>57</v>
+      </c>
+      <c r="C121">
+        <v>500</v>
+      </c>
+      <c r="D121">
+        <v>11</v>
+      </c>
+      <c r="E121">
+        <v>47</v>
+      </c>
+      <c r="F121">
+        <v>54</v>
+      </c>
+      <c r="G121">
+        <v>37</v>
+      </c>
+      <c r="H121">
+        <v>7</v>
+      </c>
+      <c r="I121">
+        <v>48</v>
+      </c>
+      <c r="J121">
+        <v>328</v>
+      </c>
+      <c r="K121">
+        <v>26</v>
+      </c>
+      <c r="L121">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>26</v>
+      </c>
+      <c r="B122" t="s">
+        <v>30</v>
+      </c>
+      <c r="C122">
+        <v>115</v>
+      </c>
+      <c r="D122">
+        <v>13</v>
+      </c>
+      <c r="E122">
+        <v>70</v>
+      </c>
+      <c r="F122">
+        <v>83</v>
+      </c>
+      <c r="G122">
+        <v>32</v>
+      </c>
+      <c r="H122">
+        <v>32</v>
+      </c>
+      <c r="I122">
+        <v>263</v>
+      </c>
+      <c r="J122">
+        <v>897</v>
+      </c>
+      <c r="K122">
+        <v>122</v>
+      </c>
+      <c r="L122">
+        <v>4.4800000000000004</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>12</v>
+      </c>
+      <c r="B123" t="s">
+        <v>20</v>
+      </c>
+      <c r="C123">
+        <v>115</v>
+      </c>
+      <c r="D123">
+        <v>15</v>
+      </c>
+      <c r="E123">
+        <v>90</v>
+      </c>
+      <c r="F123">
+        <v>93</v>
+      </c>
+      <c r="G123">
+        <v>28</v>
+      </c>
+      <c r="H123">
+        <v>30</v>
+      </c>
+      <c r="I123">
+        <v>197</v>
+      </c>
+      <c r="J123">
+        <v>842</v>
+      </c>
+      <c r="K123">
+        <v>111</v>
+      </c>
+      <c r="L123">
+        <v>5.54</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>16</v>
+      </c>
+      <c r="B124" t="s">
+        <v>49</v>
+      </c>
+      <c r="C124">
+        <v>230</v>
+      </c>
+      <c r="D124">
+        <v>13</v>
+      </c>
+      <c r="E124">
+        <v>95</v>
+      </c>
+      <c r="F124">
+        <v>72</v>
+      </c>
+      <c r="G124">
+        <v>36</v>
+      </c>
+      <c r="H124">
+        <v>32</v>
+      </c>
+      <c r="I124">
+        <v>248</v>
+      </c>
+      <c r="J124">
+        <v>758</v>
+      </c>
+      <c r="K124">
+        <v>135</v>
+      </c>
+      <c r="L124">
+        <v>4.54</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>48</v>
+      </c>
+      <c r="B125" t="s">
+        <v>29</v>
+      </c>
+      <c r="C125">
+        <v>500</v>
+      </c>
+      <c r="D125">
+        <v>29</v>
+      </c>
+      <c r="E125">
+        <v>106</v>
+      </c>
+      <c r="F125">
+        <v>92</v>
+      </c>
+      <c r="G125">
+        <v>31</v>
+      </c>
+      <c r="H125">
+        <v>83</v>
+      </c>
+      <c r="I125">
+        <v>954</v>
+      </c>
+      <c r="J125">
+        <v>1711</v>
+      </c>
+      <c r="K125">
+        <v>419</v>
+      </c>
+      <c r="L125">
+        <v>5.13</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>37</v>
+      </c>
+      <c r="B126" t="s">
+        <v>64</v>
+      </c>
+      <c r="C126">
+        <v>230</v>
+      </c>
+      <c r="D126">
+        <v>14</v>
+      </c>
+      <c r="E126">
+        <v>88</v>
+      </c>
+      <c r="F126">
+        <v>83</v>
+      </c>
+      <c r="G126">
+        <v>38</v>
+      </c>
+      <c r="H126">
+        <v>28</v>
+      </c>
+      <c r="I126">
+        <v>394</v>
+      </c>
+      <c r="J126">
+        <v>622</v>
+      </c>
+      <c r="K126">
+        <v>70</v>
+      </c>
+      <c r="L126">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>16</v>
+      </c>
+      <c r="B127" t="s">
+        <v>30</v>
+      </c>
+      <c r="C127">
+        <v>500</v>
+      </c>
+      <c r="D127">
+        <v>31</v>
+      </c>
+      <c r="E127">
+        <v>113</v>
+      </c>
+      <c r="F127">
+        <v>91</v>
+      </c>
+      <c r="G127">
+        <v>34</v>
+      </c>
+      <c r="H127">
+        <v>96</v>
+      </c>
+      <c r="I127">
+        <v>724</v>
+      </c>
+      <c r="J127">
+        <v>942</v>
+      </c>
+      <c r="K127">
+        <v>402</v>
+      </c>
+      <c r="L127">
+        <v>9.6199999999999992</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>40</v>
+      </c>
+      <c r="B128" t="s">
+        <v>65</v>
+      </c>
+      <c r="C128">
+        <v>115</v>
+      </c>
+      <c r="D128">
+        <v>2</v>
+      </c>
+      <c r="E128">
+        <v>50</v>
+      </c>
+      <c r="F128">
+        <v>72</v>
+      </c>
+      <c r="G128">
+        <v>30</v>
+      </c>
+      <c r="H128">
+        <v>20</v>
+      </c>
+      <c r="I128">
+        <v>122</v>
+      </c>
+      <c r="J128">
+        <v>460</v>
+      </c>
+      <c r="K128">
+        <v>14</v>
+      </c>
+      <c r="L128">
+        <v>2.0499999999999998</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>41</v>
+      </c>
+      <c r="B129" t="s">
+        <v>45</v>
+      </c>
+      <c r="C129">
+        <v>500</v>
+      </c>
+      <c r="D129">
+        <v>17</v>
+      </c>
+      <c r="E129">
+        <v>94</v>
+      </c>
+      <c r="F129">
+        <v>83</v>
+      </c>
+      <c r="G129">
+        <v>26</v>
+      </c>
+      <c r="H129">
+        <v>21</v>
+      </c>
+      <c r="I129">
+        <v>349</v>
+      </c>
+      <c r="J129">
+        <v>497</v>
+      </c>
+      <c r="K129">
+        <v>176</v>
+      </c>
+      <c r="L129">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>43</v>
+      </c>
+      <c r="B130" t="s">
+        <v>51</v>
+      </c>
+      <c r="C130">
+        <v>230</v>
+      </c>
+      <c r="D130">
+        <v>21</v>
+      </c>
+      <c r="E130">
+        <v>104</v>
+      </c>
+      <c r="F130">
+        <v>114</v>
+      </c>
+      <c r="G130">
+        <v>32</v>
+      </c>
+      <c r="H130">
+        <v>69</v>
+      </c>
+      <c r="I130">
+        <v>930</v>
+      </c>
+      <c r="J130">
+        <v>1245</v>
+      </c>
+      <c r="K130">
+        <v>459</v>
+      </c>
+      <c r="L130">
+        <v>10.39</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>42</v>
+      </c>
+      <c r="B131" t="s">
+        <v>58</v>
+      </c>
+      <c r="C131">
+        <v>115</v>
+      </c>
+      <c r="D131">
+        <v>22</v>
+      </c>
+      <c r="E131">
+        <v>78</v>
+      </c>
+      <c r="F131">
+        <v>94</v>
+      </c>
+      <c r="G131">
+        <v>38</v>
+      </c>
+      <c r="H131">
+        <v>45</v>
+      </c>
+      <c r="I131">
+        <v>345</v>
+      </c>
+      <c r="J131">
+        <v>558</v>
+      </c>
+      <c r="K131">
+        <v>152</v>
+      </c>
+      <c r="L131">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>24</v>
+      </c>
+      <c r="B132" t="s">
+        <v>64</v>
+      </c>
+      <c r="C132">
+        <v>230</v>
+      </c>
+      <c r="D132">
+        <v>22</v>
+      </c>
+      <c r="E132">
+        <v>84</v>
+      </c>
+      <c r="F132">
+        <v>81</v>
+      </c>
+      <c r="G132">
+        <v>29</v>
+      </c>
+      <c r="H132">
+        <v>33</v>
+      </c>
+      <c r="I132">
+        <v>154</v>
+      </c>
+      <c r="J132">
+        <v>889</v>
+      </c>
+      <c r="K132">
+        <v>63</v>
+      </c>
+      <c r="L132">
+        <v>4.9800000000000004</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>33</v>
+      </c>
+      <c r="B133" t="s">
+        <v>18</v>
+      </c>
+      <c r="C133">
+        <v>115</v>
+      </c>
+      <c r="D133">
+        <v>33</v>
+      </c>
+      <c r="E133">
+        <v>94</v>
+      </c>
+      <c r="F133">
+        <v>93</v>
+      </c>
+      <c r="G133">
+        <v>35</v>
+      </c>
+      <c r="H133">
+        <v>40</v>
+      </c>
+      <c r="I133">
+        <v>936</v>
+      </c>
+      <c r="J133">
+        <v>1255</v>
+      </c>
+      <c r="K133">
+        <v>241</v>
+      </c>
+      <c r="L133">
+        <v>8.42</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>19</v>
+      </c>
+      <c r="B134" t="s">
+        <v>18</v>
+      </c>
+      <c r="C134">
+        <v>115</v>
+      </c>
+      <c r="D134">
+        <v>6</v>
+      </c>
+      <c r="E134">
+        <v>72</v>
+      </c>
+      <c r="F134">
+        <v>62</v>
+      </c>
+      <c r="G134">
+        <v>36</v>
+      </c>
+      <c r="H134">
+        <v>20</v>
+      </c>
+      <c r="I134">
+        <v>108</v>
+      </c>
+      <c r="J134">
+        <v>248</v>
+      </c>
+      <c r="K134">
+        <v>14</v>
+      </c>
+      <c r="L134">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>37</v>
+      </c>
+      <c r="B135" t="s">
+        <v>44</v>
+      </c>
+      <c r="C135">
+        <v>230</v>
+      </c>
+      <c r="D135">
+        <v>23</v>
+      </c>
+      <c r="E135">
+        <v>109</v>
+      </c>
+      <c r="F135">
+        <v>89</v>
+      </c>
+      <c r="G135">
+        <v>41</v>
+      </c>
+      <c r="H135">
+        <v>59</v>
+      </c>
+      <c r="I135">
+        <v>562</v>
+      </c>
+      <c r="J135">
+        <v>1085</v>
+      </c>
+      <c r="K135">
+        <v>322</v>
+      </c>
+      <c r="L135">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>37</v>
+      </c>
+      <c r="B136" t="s">
+        <v>52</v>
+      </c>
+      <c r="C136">
+        <v>500</v>
+      </c>
+      <c r="D136">
+        <v>1</v>
+      </c>
+      <c r="E136">
+        <v>76</v>
+      </c>
+      <c r="F136">
+        <v>50</v>
+      </c>
+      <c r="G136">
+        <v>26</v>
+      </c>
+      <c r="H136">
+        <v>23</v>
+      </c>
+      <c r="I136">
+        <v>45</v>
+      </c>
+      <c r="J136">
+        <v>138</v>
+      </c>
+      <c r="K136">
+        <v>22</v>
+      </c>
+      <c r="L136">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>43</v>
+      </c>
+      <c r="B137" t="s">
+        <v>17</v>
+      </c>
+      <c r="C137">
+        <v>500</v>
+      </c>
+      <c r="D137">
+        <v>1</v>
+      </c>
+      <c r="E137">
+        <v>55</v>
+      </c>
+      <c r="F137">
+        <v>56</v>
+      </c>
+      <c r="G137">
+        <v>38</v>
+      </c>
+      <c r="H137">
+        <v>20</v>
+      </c>
+      <c r="I137">
+        <v>84</v>
+      </c>
+      <c r="J137">
+        <v>281</v>
+      </c>
+      <c r="K137">
+        <v>73</v>
+      </c>
+      <c r="L137">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>42</v>
+      </c>
+      <c r="B138" t="s">
+        <v>51</v>
+      </c>
+      <c r="C138">
+        <v>115</v>
+      </c>
+      <c r="D138">
+        <v>11</v>
+      </c>
+      <c r="E138">
+        <v>68</v>
+      </c>
+      <c r="F138">
+        <v>54</v>
+      </c>
+      <c r="G138">
+        <v>35</v>
+      </c>
+      <c r="H138">
+        <v>14</v>
+      </c>
+      <c r="I138">
+        <v>37</v>
+      </c>
+      <c r="J138">
+        <v>157</v>
+      </c>
+      <c r="K138">
+        <v>58</v>
+      </c>
+      <c r="L138">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>42</v>
+      </c>
+      <c r="B139" t="s">
+        <v>38</v>
+      </c>
+      <c r="C139">
+        <v>230</v>
+      </c>
+      <c r="D139">
+        <v>37</v>
+      </c>
+      <c r="E139">
+        <v>104</v>
+      </c>
+      <c r="F139">
+        <v>117</v>
+      </c>
+      <c r="G139">
+        <v>38</v>
+      </c>
+      <c r="H139">
+        <v>95</v>
+      </c>
+      <c r="I139">
+        <v>889</v>
+      </c>
+      <c r="J139">
+        <v>1147</v>
+      </c>
+      <c r="K139">
+        <v>174</v>
+      </c>
+      <c r="L139">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>14</v>
+      </c>
+      <c r="B140" t="s">
+        <v>17</v>
+      </c>
+      <c r="C140">
+        <v>500</v>
+      </c>
+      <c r="D140">
+        <v>24</v>
+      </c>
+      <c r="E140">
+        <v>99</v>
+      </c>
+      <c r="F140">
+        <v>103</v>
+      </c>
+      <c r="G140">
+        <v>40</v>
+      </c>
+      <c r="H140">
+        <v>54</v>
+      </c>
+      <c r="I140">
+        <v>372</v>
+      </c>
+      <c r="J140">
+        <v>1634</v>
+      </c>
+      <c r="K140">
+        <v>494</v>
+      </c>
+      <c r="L140">
+        <v>5.27</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>42</v>
+      </c>
+      <c r="B141" t="s">
+        <v>56</v>
+      </c>
+      <c r="C141">
+        <v>500</v>
+      </c>
+      <c r="D141">
+        <v>27</v>
+      </c>
+      <c r="E141">
+        <v>104</v>
+      </c>
+      <c r="F141">
+        <v>85</v>
+      </c>
+      <c r="G141">
+        <v>41</v>
+      </c>
+      <c r="H141">
+        <v>88</v>
+      </c>
+      <c r="I141">
+        <v>376</v>
+      </c>
+      <c r="J141">
+        <v>1426</v>
+      </c>
+      <c r="K141">
+        <v>290</v>
+      </c>
+      <c r="L141">
+        <v>6.69</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>21</v>
+      </c>
+      <c r="B142" t="s">
+        <v>36</v>
+      </c>
+      <c r="C142">
+        <v>115</v>
+      </c>
+      <c r="D142">
+        <v>24</v>
+      </c>
+      <c r="E142">
+        <v>90</v>
+      </c>
+      <c r="F142">
+        <v>65</v>
+      </c>
+      <c r="G142">
+        <v>29</v>
+      </c>
+      <c r="H142">
+        <v>21</v>
+      </c>
+      <c r="I142">
+        <v>143</v>
+      </c>
+      <c r="J142">
+        <v>717</v>
+      </c>
+      <c r="K142">
+        <v>157</v>
+      </c>
+      <c r="L142">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>14</v>
+      </c>
+      <c r="B143" t="s">
+        <v>23</v>
+      </c>
+      <c r="C143">
+        <v>500</v>
+      </c>
+      <c r="D143">
+        <v>23</v>
+      </c>
+      <c r="E143">
+        <v>88</v>
+      </c>
+      <c r="F143">
+        <v>67</v>
+      </c>
+      <c r="G143">
+        <v>39</v>
+      </c>
+      <c r="H143">
+        <v>41</v>
+      </c>
+      <c r="I143">
+        <v>328</v>
+      </c>
+      <c r="J143">
+        <v>650</v>
+      </c>
+      <c r="K143">
+        <v>72</v>
+      </c>
+      <c r="L143">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>43</v>
+      </c>
+      <c r="B144" t="s">
+        <v>63</v>
+      </c>
+      <c r="C144">
+        <v>230</v>
+      </c>
+      <c r="D144">
+        <v>21</v>
+      </c>
+      <c r="E144">
+        <v>100</v>
+      </c>
+      <c r="F144">
+        <v>110</v>
+      </c>
+      <c r="G144">
+        <v>43</v>
+      </c>
+      <c r="H144">
+        <v>65</v>
+      </c>
+      <c r="I144">
+        <v>525</v>
+      </c>
+      <c r="J144">
+        <v>1007</v>
+      </c>
+      <c r="K144">
+        <v>430</v>
+      </c>
+      <c r="L144">
+        <v>10.79</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>33</v>
+      </c>
+      <c r="B145" t="s">
+        <v>64</v>
+      </c>
+      <c r="C145">
+        <v>115</v>
+      </c>
+      <c r="D145">
+        <v>6</v>
+      </c>
+      <c r="E145">
+        <v>58</v>
+      </c>
+      <c r="F145">
+        <v>49</v>
+      </c>
+      <c r="G145">
+        <v>30</v>
+      </c>
+      <c r="H145">
+        <v>19</v>
+      </c>
+      <c r="I145">
+        <v>122</v>
+      </c>
+      <c r="J145">
+        <v>341</v>
+      </c>
+      <c r="K145">
+        <v>78</v>
+      </c>
+      <c r="L145">
+        <v>2.2400000000000002</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>46</v>
+      </c>
+      <c r="B146" t="s">
+        <v>18</v>
+      </c>
+      <c r="C146">
+        <v>230</v>
+      </c>
+      <c r="D146">
+        <v>32</v>
+      </c>
+      <c r="E146">
+        <v>117</v>
+      </c>
+      <c r="F146">
+        <v>88</v>
+      </c>
+      <c r="G146">
+        <v>39</v>
+      </c>
+      <c r="H146">
+        <v>46</v>
+      </c>
+      <c r="I146">
+        <v>949</v>
+      </c>
+      <c r="J146">
+        <v>1036</v>
+      </c>
+      <c r="K146">
+        <v>387</v>
+      </c>
+      <c r="L146">
+        <v>6.51</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>21</v>
+      </c>
+      <c r="B147" t="s">
+        <v>50</v>
+      </c>
+      <c r="C147">
+        <v>115</v>
+      </c>
+      <c r="D147">
+        <v>23</v>
+      </c>
+      <c r="E147">
+        <v>114</v>
+      </c>
+      <c r="F147">
+        <v>85</v>
+      </c>
+      <c r="G147">
+        <v>31</v>
+      </c>
+      <c r="H147">
+        <v>43</v>
+      </c>
+      <c r="I147">
+        <v>407</v>
+      </c>
+      <c r="J147">
+        <v>1110</v>
+      </c>
+      <c r="K147">
+        <v>174</v>
+      </c>
+      <c r="L147">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>19</v>
+      </c>
+      <c r="B148" t="s">
+        <v>64</v>
+      </c>
+      <c r="C148">
+        <v>115</v>
+      </c>
+      <c r="D148">
+        <v>22</v>
+      </c>
+      <c r="E148">
+        <v>116</v>
+      </c>
+      <c r="F148">
+        <v>100</v>
+      </c>
+      <c r="G148">
+        <v>34</v>
+      </c>
+      <c r="H148">
+        <v>95</v>
+      </c>
+      <c r="I148">
+        <v>553</v>
+      </c>
+      <c r="J148">
+        <v>1163</v>
+      </c>
+      <c r="K148">
+        <v>228</v>
+      </c>
+      <c r="L148">
+        <v>11.72</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>33</v>
+      </c>
+      <c r="B149" t="s">
+        <v>54</v>
+      </c>
+      <c r="C149">
+        <v>230</v>
+      </c>
+      <c r="D149">
+        <v>4</v>
+      </c>
+      <c r="E149">
+        <v>61</v>
+      </c>
+      <c r="F149">
+        <v>55</v>
+      </c>
+      <c r="G149">
+        <v>28</v>
+      </c>
+      <c r="H149">
+        <v>7</v>
+      </c>
+      <c r="I149">
+        <v>18</v>
+      </c>
+      <c r="J149">
+        <v>404</v>
+      </c>
+      <c r="K149">
+        <v>41</v>
+      </c>
+      <c r="L149">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>16</v>
+      </c>
+      <c r="B150" t="s">
+        <v>29</v>
+      </c>
+      <c r="C150">
+        <v>500</v>
+      </c>
+      <c r="D150">
+        <v>31</v>
+      </c>
+      <c r="E150">
+        <v>97</v>
+      </c>
+      <c r="F150">
+        <v>105</v>
+      </c>
+      <c r="G150">
+        <v>35</v>
+      </c>
+      <c r="H150">
+        <v>55</v>
+      </c>
+      <c r="I150">
+        <v>445</v>
+      </c>
+      <c r="J150">
+        <v>1569</v>
+      </c>
+      <c r="K150">
+        <v>312</v>
+      </c>
+      <c r="L150">
+        <v>9.3699999999999992</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>40</v>
+      </c>
+      <c r="B151" t="s">
+        <v>62</v>
+      </c>
+      <c r="C151">
+        <v>115</v>
+      </c>
+      <c r="D151">
+        <v>29</v>
+      </c>
+      <c r="E151">
+        <v>114</v>
+      </c>
+      <c r="F151">
+        <v>96</v>
+      </c>
+      <c r="G151">
+        <v>43</v>
+      </c>
+      <c r="H151">
+        <v>88</v>
+      </c>
+      <c r="I151">
+        <v>838</v>
+      </c>
+      <c r="J151">
+        <v>811</v>
+      </c>
+      <c r="K151">
+        <v>478</v>
+      </c>
+      <c r="L151">
+        <v>8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>37</v>
+      </c>
+      <c r="B152" t="s">
+        <v>60</v>
+      </c>
+      <c r="C152">
+        <v>115</v>
+      </c>
+      <c r="D152">
+        <v>8</v>
+      </c>
+      <c r="E152">
+        <v>40</v>
+      </c>
+      <c r="F152">
+        <v>73</v>
+      </c>
+      <c r="G152">
+        <v>31</v>
+      </c>
+      <c r="H152">
+        <v>7</v>
+      </c>
+      <c r="I152">
+        <v>147</v>
+      </c>
+      <c r="J152">
+        <v>301</v>
+      </c>
+      <c r="K152">
+        <v>26</v>
+      </c>
+      <c r="L152">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>48</v>
+      </c>
+      <c r="B153" t="s">
+        <v>50</v>
+      </c>
+      <c r="C153">
+        <v>230</v>
+      </c>
+      <c r="D153">
+        <v>22</v>
+      </c>
+      <c r="E153">
+        <v>113</v>
+      </c>
+      <c r="F153">
+        <v>109</v>
+      </c>
+      <c r="G153">
+        <v>42</v>
+      </c>
+      <c r="H153">
+        <v>70</v>
+      </c>
+      <c r="I153">
+        <v>822</v>
+      </c>
+      <c r="J153">
+        <v>1314</v>
+      </c>
+      <c r="K153">
+        <v>459</v>
+      </c>
+      <c r="L153">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>12</v>
+      </c>
+      <c r="B154" t="s">
+        <v>61</v>
+      </c>
+      <c r="C154">
+        <v>500</v>
+      </c>
+      <c r="D154">
+        <v>3</v>
+      </c>
+      <c r="E154">
+        <v>46</v>
+      </c>
+      <c r="F154">
+        <v>61</v>
+      </c>
+      <c r="G154">
+        <v>38</v>
+      </c>
+      <c r="H154">
+        <v>5</v>
+      </c>
+      <c r="I154">
+        <v>123</v>
+      </c>
+      <c r="J154">
+        <v>463</v>
+      </c>
+      <c r="K154">
+        <v>50</v>
+      </c>
+      <c r="L154">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>48</v>
+      </c>
+      <c r="B155" t="s">
+        <v>20</v>
+      </c>
+      <c r="C155">
+        <v>500</v>
+      </c>
+      <c r="D155">
+        <v>21</v>
+      </c>
+      <c r="E155">
+        <v>98</v>
+      </c>
+      <c r="F155">
+        <v>82</v>
+      </c>
+      <c r="G155">
+        <v>33</v>
+      </c>
+      <c r="H155">
+        <v>40</v>
+      </c>
+      <c r="I155">
+        <v>179</v>
+      </c>
+      <c r="J155">
+        <v>638</v>
+      </c>
+      <c r="K155">
+        <v>182</v>
+      </c>
+      <c r="L155">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>24</v>
+      </c>
+      <c r="B156" t="s">
+        <v>58</v>
+      </c>
+      <c r="C156">
+        <v>230</v>
+      </c>
+      <c r="D156">
+        <v>34</v>
+      </c>
+      <c r="E156">
+        <v>94</v>
+      </c>
+      <c r="F156">
+        <v>94</v>
+      </c>
+      <c r="G156">
+        <v>38</v>
+      </c>
+      <c r="H156">
+        <v>64</v>
+      </c>
+      <c r="I156">
+        <v>972</v>
+      </c>
+      <c r="J156">
+        <v>1417</v>
+      </c>
+      <c r="K156">
+        <v>402</v>
+      </c>
+      <c r="L156">
+        <v>10.14</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>40</v>
+      </c>
+      <c r="B157" t="s">
+        <v>35</v>
+      </c>
+      <c r="C157">
+        <v>500</v>
+      </c>
+      <c r="D157">
+        <v>10</v>
+      </c>
+      <c r="E157">
+        <v>77</v>
+      </c>
+      <c r="F157">
+        <v>73</v>
+      </c>
+      <c r="G157">
+        <v>30</v>
+      </c>
+      <c r="H157">
+        <v>5</v>
+      </c>
+      <c r="I157">
+        <v>121</v>
+      </c>
+      <c r="J157">
+        <v>447</v>
+      </c>
+      <c r="K157">
+        <v>27</v>
+      </c>
+      <c r="L157">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>43</v>
+      </c>
+      <c r="B158" t="s">
+        <v>20</v>
+      </c>
+      <c r="C158">
+        <v>500</v>
+      </c>
+      <c r="D158">
+        <v>24</v>
+      </c>
+      <c r="E158">
+        <v>94</v>
+      </c>
+      <c r="F158">
+        <v>100</v>
+      </c>
+      <c r="G158">
+        <v>32</v>
+      </c>
+      <c r="H158">
+        <v>74</v>
+      </c>
+      <c r="I158">
+        <v>466</v>
+      </c>
+      <c r="J158">
+        <v>1526</v>
+      </c>
+      <c r="K158">
+        <v>163</v>
+      </c>
+      <c r="L158">
+        <v>9.31</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>46</v>
+      </c>
+      <c r="B159" t="s">
+        <v>57</v>
+      </c>
+      <c r="C159">
+        <v>230</v>
+      </c>
+      <c r="D159">
+        <v>13</v>
+      </c>
+      <c r="E159">
+        <v>78</v>
+      </c>
+      <c r="F159">
+        <v>78</v>
+      </c>
+      <c r="G159">
+        <v>31</v>
+      </c>
+      <c r="H159">
+        <v>30</v>
+      </c>
+      <c r="I159">
+        <v>247</v>
+      </c>
+      <c r="J159">
+        <v>582</v>
+      </c>
+      <c r="K159">
+        <v>166</v>
+      </c>
+      <c r="L159">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>42</v>
+      </c>
+      <c r="B160" t="s">
+        <v>45</v>
+      </c>
+      <c r="C160">
+        <v>230</v>
+      </c>
+      <c r="D160">
+        <v>5</v>
+      </c>
+      <c r="E160">
+        <v>65</v>
+      </c>
+      <c r="F160">
+        <v>72</v>
+      </c>
+      <c r="G160">
+        <v>36</v>
+      </c>
+      <c r="H160">
+        <v>11</v>
+      </c>
+      <c r="I160">
+        <v>129</v>
+      </c>
+      <c r="J160">
+        <v>266</v>
+      </c>
+      <c r="K160">
+        <v>36</v>
+      </c>
+      <c r="L160">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>26</v>
+      </c>
+      <c r="B161" t="s">
+        <v>47</v>
+      </c>
+      <c r="C161">
+        <v>500</v>
+      </c>
+      <c r="D161">
+        <v>27</v>
+      </c>
+      <c r="E161">
+        <v>89</v>
+      </c>
+      <c r="F161">
+        <v>66</v>
+      </c>
+      <c r="G161">
+        <v>36</v>
+      </c>
+      <c r="H161">
+        <v>46</v>
+      </c>
+      <c r="I161">
+        <v>374</v>
+      </c>
+      <c r="J161">
+        <v>428</v>
+      </c>
+      <c r="K161">
+        <v>127</v>
+      </c>
+      <c r="L161">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>48</v>
+      </c>
+      <c r="B162" t="s">
+        <v>63</v>
+      </c>
+      <c r="C162">
+        <v>115</v>
+      </c>
+      <c r="D162">
+        <v>1</v>
+      </c>
+      <c r="E162">
+        <v>79</v>
+      </c>
+      <c r="F162">
+        <v>45</v>
+      </c>
+      <c r="G162">
+        <v>36</v>
+      </c>
+      <c r="H162">
+        <v>13</v>
+      </c>
+      <c r="I162">
+        <v>90</v>
+      </c>
+      <c r="J162">
+        <v>244</v>
+      </c>
+      <c r="K162">
+        <v>33</v>
+      </c>
+      <c r="L162">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>40</v>
+      </c>
+      <c r="B163" t="s">
+        <v>64</v>
+      </c>
+      <c r="C163">
+        <v>115</v>
+      </c>
+      <c r="D163">
+        <v>24</v>
+      </c>
+      <c r="E163">
+        <v>89</v>
+      </c>
+      <c r="F163">
+        <v>72</v>
+      </c>
+      <c r="G163">
+        <v>31</v>
+      </c>
+      <c r="H163">
+        <v>32</v>
+      </c>
+      <c r="I163">
+        <v>388</v>
+      </c>
+      <c r="J163">
+        <v>587</v>
+      </c>
+      <c r="K163">
+        <v>113</v>
+      </c>
+      <c r="L163">
+        <v>5.13</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>16</v>
+      </c>
+      <c r="B164" t="s">
+        <v>51</v>
+      </c>
+      <c r="C164">
+        <v>115</v>
+      </c>
+      <c r="D164">
+        <v>23</v>
+      </c>
+      <c r="E164">
+        <v>97</v>
+      </c>
+      <c r="F164">
+        <v>69</v>
+      </c>
+      <c r="G164">
+        <v>31</v>
+      </c>
+      <c r="H164">
+        <v>38</v>
+      </c>
+      <c r="I164">
+        <v>365</v>
+      </c>
+      <c r="J164">
+        <v>798</v>
+      </c>
+      <c r="K164">
+        <v>87</v>
+      </c>
+      <c r="L164">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>41</v>
+      </c>
+      <c r="B165" t="s">
+        <v>13</v>
+      </c>
+      <c r="C165">
+        <v>115</v>
+      </c>
+      <c r="D165">
+        <v>36</v>
+      </c>
+      <c r="E165">
+        <v>90</v>
+      </c>
+      <c r="F165">
+        <v>113</v>
+      </c>
+      <c r="G165">
+        <v>32</v>
+      </c>
+      <c r="H165">
+        <v>69</v>
+      </c>
+      <c r="I165">
+        <v>541</v>
+      </c>
+      <c r="J165">
+        <v>915</v>
+      </c>
+      <c r="K165">
+        <v>279</v>
+      </c>
+      <c r="L165">
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>26</v>
+      </c>
+      <c r="B166" t="s">
+        <v>34</v>
+      </c>
+      <c r="C166">
+        <v>115</v>
+      </c>
+      <c r="D166">
+        <v>2</v>
+      </c>
+      <c r="E166">
+        <v>74</v>
+      </c>
+      <c r="F166">
+        <v>61</v>
+      </c>
+      <c r="G166">
+        <v>32</v>
+      </c>
+      <c r="H166">
+        <v>17</v>
+      </c>
+      <c r="I166">
+        <v>67</v>
+      </c>
+      <c r="J166">
+        <v>374</v>
+      </c>
+      <c r="K166">
+        <v>37</v>
+      </c>
+      <c r="L166">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>41</v>
+      </c>
+      <c r="B167" t="s">
+        <v>63</v>
+      </c>
+      <c r="C167">
+        <v>115</v>
+      </c>
+      <c r="D167">
+        <v>20</v>
+      </c>
+      <c r="E167">
+        <v>91</v>
+      </c>
+      <c r="F167">
+        <v>74</v>
+      </c>
+      <c r="G167">
+        <v>26</v>
+      </c>
+      <c r="H167">
+        <v>40</v>
+      </c>
+      <c r="I167">
+        <v>207</v>
+      </c>
+      <c r="J167">
+        <v>540</v>
+      </c>
+      <c r="K167">
+        <v>179</v>
+      </c>
+      <c r="L167">
+        <v>5.16</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>12</v>
+      </c>
+      <c r="B168" t="s">
+        <v>25</v>
+      </c>
+      <c r="C168">
+        <v>500</v>
+      </c>
+      <c r="D168">
+        <v>10</v>
+      </c>
+      <c r="E168">
+        <v>75</v>
+      </c>
+      <c r="F168">
+        <v>92</v>
+      </c>
+      <c r="G168">
+        <v>28</v>
+      </c>
+      <c r="H168">
+        <v>27</v>
+      </c>
+      <c r="I168">
+        <v>200</v>
+      </c>
+      <c r="J168">
+        <v>876</v>
+      </c>
+      <c r="K168">
+        <v>160</v>
+      </c>
+      <c r="L168">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>16</v>
+      </c>
+      <c r="B169" t="s">
+        <v>58</v>
+      </c>
+      <c r="C169">
+        <v>115</v>
+      </c>
+      <c r="D169">
+        <v>20</v>
+      </c>
+      <c r="E169">
+        <v>70</v>
+      </c>
+      <c r="F169">
+        <v>87</v>
+      </c>
+      <c r="G169">
+        <v>30</v>
+      </c>
+      <c r="H169">
+        <v>32</v>
+      </c>
+      <c r="I169">
+        <v>156</v>
+      </c>
+      <c r="J169">
+        <v>671</v>
+      </c>
+      <c r="K169">
+        <v>164</v>
+      </c>
+      <c r="L169">
+        <v>4.91</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>12</v>
+      </c>
+      <c r="B170" t="s">
+        <v>30</v>
+      </c>
+      <c r="C170">
+        <v>500</v>
+      </c>
+      <c r="D170">
+        <v>34</v>
+      </c>
+      <c r="E170">
+        <v>95</v>
+      </c>
+      <c r="F170">
+        <v>103</v>
+      </c>
+      <c r="G170">
+        <v>34</v>
+      </c>
+      <c r="H170">
+        <v>81</v>
+      </c>
+      <c r="I170">
+        <v>808</v>
+      </c>
+      <c r="J170">
+        <v>1927</v>
+      </c>
+      <c r="K170">
+        <v>266</v>
+      </c>
+      <c r="L170">
+        <v>11.83</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>21</v>
+      </c>
+      <c r="B171" t="s">
+        <v>18</v>
+      </c>
+      <c r="C171">
+        <v>230</v>
+      </c>
+      <c r="D171">
+        <v>29</v>
+      </c>
+      <c r="E171">
+        <v>96</v>
+      </c>
+      <c r="F171">
+        <v>70</v>
+      </c>
+      <c r="G171">
+        <v>26</v>
+      </c>
+      <c r="H171">
+        <v>24</v>
+      </c>
+      <c r="I171">
+        <v>316</v>
+      </c>
+      <c r="J171">
+        <v>892</v>
+      </c>
+      <c r="K171">
+        <v>158</v>
+      </c>
+      <c r="L171">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>41</v>
+      </c>
+      <c r="B172" t="s">
+        <v>61</v>
+      </c>
+      <c r="C172">
+        <v>115</v>
+      </c>
+      <c r="D172">
+        <v>10</v>
+      </c>
+      <c r="E172">
+        <v>94</v>
+      </c>
+      <c r="F172">
+        <v>87</v>
+      </c>
+      <c r="G172">
+        <v>27</v>
+      </c>
+      <c r="H172">
+        <v>21</v>
+      </c>
+      <c r="I172">
+        <v>110</v>
+      </c>
+      <c r="J172">
+        <v>536</v>
+      </c>
+      <c r="K172">
+        <v>98</v>
+      </c>
+      <c r="L172">
+        <v>4.87</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>26</v>
+      </c>
+      <c r="B173" t="s">
+        <v>32</v>
+      </c>
+      <c r="C173">
+        <v>500</v>
+      </c>
+      <c r="D173">
+        <v>1</v>
+      </c>
+      <c r="E173">
+        <v>69</v>
+      </c>
+      <c r="F173">
+        <v>62</v>
+      </c>
+      <c r="G173">
+        <v>39</v>
+      </c>
+      <c r="H173">
+        <v>18</v>
+      </c>
+      <c r="I173">
+        <v>145</v>
+      </c>
+      <c r="J173">
+        <v>111</v>
+      </c>
+      <c r="K173">
+        <v>74</v>
+      </c>
+      <c r="L173">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>46</v>
+      </c>
+      <c r="B174" t="s">
+        <v>45</v>
+      </c>
+      <c r="C174">
+        <v>230</v>
+      </c>
+      <c r="D174">
+        <v>25</v>
+      </c>
+      <c r="E174">
+        <v>91</v>
+      </c>
+      <c r="F174">
+        <v>93</v>
+      </c>
+      <c r="G174">
+        <v>29</v>
+      </c>
+      <c r="H174">
+        <v>29</v>
+      </c>
+      <c r="I174">
+        <v>363</v>
+      </c>
+      <c r="J174">
+        <v>665</v>
+      </c>
+      <c r="K174">
+        <v>196</v>
+      </c>
+      <c r="L174">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>40</v>
+      </c>
+      <c r="B175" t="s">
+        <v>22</v>
+      </c>
+      <c r="C175">
+        <v>115</v>
+      </c>
+      <c r="D175">
+        <v>7</v>
+      </c>
+      <c r="E175">
+        <v>64</v>
+      </c>
+      <c r="F175">
+        <v>47</v>
+      </c>
+      <c r="G175">
+        <v>30</v>
+      </c>
+      <c r="H175">
+        <v>8</v>
+      </c>
+      <c r="I175">
+        <v>149</v>
+      </c>
+      <c r="J175">
+        <v>411</v>
+      </c>
+      <c r="K175">
+        <v>72</v>
+      </c>
+      <c r="L175">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>19</v>
+      </c>
+      <c r="B176" t="s">
+        <v>23</v>
+      </c>
+      <c r="C176">
+        <v>115</v>
+      </c>
+      <c r="D176">
+        <v>1</v>
+      </c>
+      <c r="E176">
+        <v>53</v>
+      </c>
+      <c r="F176">
+        <v>67</v>
+      </c>
+      <c r="G176">
+        <v>31</v>
+      </c>
+      <c r="H176">
+        <v>24</v>
+      </c>
+      <c r="I176">
+        <v>132</v>
+      </c>
+      <c r="J176">
+        <v>312</v>
+      </c>
+      <c r="K176">
+        <v>32</v>
+      </c>
+      <c r="L176">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>40</v>
+      </c>
+      <c r="B177" t="s">
+        <v>23</v>
+      </c>
+      <c r="C177">
+        <v>230</v>
+      </c>
+      <c r="D177">
+        <v>16</v>
+      </c>
+      <c r="E177">
+        <v>95</v>
+      </c>
+      <c r="F177">
+        <v>81</v>
+      </c>
+      <c r="G177">
+        <v>25</v>
+      </c>
+      <c r="H177">
+        <v>38</v>
+      </c>
+      <c r="I177">
+        <v>381</v>
+      </c>
+      <c r="J177">
+        <v>485</v>
+      </c>
+      <c r="K177">
+        <v>147</v>
+      </c>
+      <c r="L177">
+        <v>4.2300000000000004</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>41</v>
+      </c>
+      <c r="B178" t="s">
+        <v>59</v>
+      </c>
+      <c r="C178">
+        <v>500</v>
+      </c>
+      <c r="D178">
+        <v>21</v>
+      </c>
+      <c r="E178">
+        <v>117</v>
+      </c>
+      <c r="F178">
+        <v>118</v>
+      </c>
+      <c r="G178">
+        <v>39</v>
+      </c>
+      <c r="H178">
+        <v>52</v>
+      </c>
+      <c r="I178">
+        <v>782</v>
+      </c>
+      <c r="J178">
+        <v>1816</v>
+      </c>
+      <c r="K178">
+        <v>415</v>
+      </c>
+      <c r="L178">
+        <v>7.57</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>43</v>
+      </c>
+      <c r="B179" t="s">
+        <v>39</v>
+      </c>
+      <c r="C179">
+        <v>230</v>
+      </c>
+      <c r="D179">
+        <v>14</v>
+      </c>
+      <c r="E179">
+        <v>87</v>
+      </c>
+      <c r="F179">
+        <v>94</v>
+      </c>
+      <c r="G179">
+        <v>36</v>
+      </c>
+      <c r="H179">
+        <v>36</v>
+      </c>
+      <c r="I179">
+        <v>228</v>
+      </c>
+      <c r="J179">
+        <v>415</v>
+      </c>
+      <c r="K179">
+        <v>68</v>
+      </c>
+      <c r="L179">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>33</v>
+      </c>
+      <c r="B180" t="s">
+        <v>22</v>
+      </c>
+      <c r="C180">
+        <v>500</v>
+      </c>
+      <c r="D180">
+        <v>17</v>
+      </c>
+      <c r="E180">
+        <v>86</v>
+      </c>
+      <c r="F180">
+        <v>72</v>
+      </c>
+      <c r="G180">
+        <v>38</v>
+      </c>
+      <c r="H180">
+        <v>47</v>
+      </c>
+      <c r="I180">
+        <v>158</v>
+      </c>
+      <c r="J180">
+        <v>545</v>
+      </c>
+      <c r="K180">
+        <v>192</v>
+      </c>
+      <c r="L180">
+        <v>5.15</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>42</v>
+      </c>
+      <c r="B181" t="s">
+        <v>30</v>
+      </c>
+      <c r="C181">
+        <v>230</v>
+      </c>
+      <c r="D181">
+        <v>19</v>
+      </c>
+      <c r="E181">
+        <v>92</v>
+      </c>
+      <c r="F181">
+        <v>88</v>
+      </c>
+      <c r="G181">
+        <v>32</v>
+      </c>
+      <c r="H181">
+        <v>26</v>
+      </c>
+      <c r="I181">
+        <v>286</v>
+      </c>
+      <c r="J181">
+        <v>993</v>
+      </c>
+      <c r="K181">
+        <v>147</v>
+      </c>
+      <c r="L181">
+        <v>5.58</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>21</v>
+      </c>
+      <c r="B182" t="s">
+        <v>63</v>
+      </c>
+      <c r="C182">
+        <v>230</v>
+      </c>
+      <c r="D182">
+        <v>24</v>
+      </c>
+      <c r="E182">
+        <v>96</v>
+      </c>
+      <c r="F182">
+        <v>71</v>
+      </c>
+      <c r="G182">
+        <v>34</v>
+      </c>
+      <c r="H182">
+        <v>29</v>
+      </c>
+      <c r="I182">
+        <v>230</v>
+      </c>
+      <c r="J182">
+        <v>813</v>
+      </c>
+      <c r="K182">
+        <v>62</v>
+      </c>
+      <c r="L182">
+        <v>5.23</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>40</v>
+      </c>
+      <c r="B183" t="s">
+        <v>66</v>
+      </c>
+      <c r="C183">
+        <v>500</v>
+      </c>
+      <c r="D183">
+        <v>17</v>
+      </c>
+      <c r="E183">
+        <v>81</v>
+      </c>
+      <c r="F183">
+        <v>87</v>
+      </c>
+      <c r="G183">
+        <v>35</v>
+      </c>
+      <c r="H183">
+        <v>40</v>
+      </c>
+      <c r="I183">
+        <v>390</v>
+      </c>
+      <c r="J183">
+        <v>945</v>
+      </c>
+      <c r="K183">
+        <v>121</v>
+      </c>
+      <c r="L183">
+        <v>4.3899999999999997</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>14</v>
+      </c>
+      <c r="B184" t="s">
+        <v>59</v>
+      </c>
+      <c r="C184">
+        <v>115</v>
+      </c>
+      <c r="D184">
+        <v>8</v>
+      </c>
+      <c r="E184">
+        <v>64</v>
+      </c>
+      <c r="F184">
+        <v>69</v>
+      </c>
+      <c r="G184">
+        <v>30</v>
+      </c>
+      <c r="H184">
+        <v>24</v>
+      </c>
+      <c r="I184">
+        <v>18</v>
+      </c>
+      <c r="J184">
+        <v>233</v>
+      </c>
+      <c r="K184">
+        <v>36</v>
+      </c>
+      <c r="L184">
+        <v>2.2400000000000002</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>48</v>
+      </c>
+      <c r="B185" t="s">
+        <v>51</v>
+      </c>
+      <c r="C185">
+        <v>500</v>
+      </c>
+      <c r="D185">
+        <v>20</v>
+      </c>
+      <c r="E185">
+        <v>91</v>
+      </c>
+      <c r="F185">
+        <v>89</v>
+      </c>
+      <c r="G185">
+        <v>35</v>
+      </c>
+      <c r="H185">
+        <v>30</v>
+      </c>
+      <c r="I185">
+        <v>146</v>
+      </c>
+      <c r="J185">
+        <v>831</v>
+      </c>
+      <c r="K185">
+        <v>96</v>
+      </c>
+      <c r="L185">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>21</v>
+      </c>
+      <c r="B186" t="s">
+        <v>15</v>
+      </c>
+      <c r="C186">
+        <v>115</v>
+      </c>
+      <c r="D186">
+        <v>4</v>
+      </c>
+      <c r="E186">
+        <v>66</v>
+      </c>
+      <c r="F186">
+        <v>54</v>
+      </c>
+      <c r="G186">
+        <v>38</v>
+      </c>
+      <c r="H186">
+        <v>15</v>
+      </c>
+      <c r="I186">
+        <v>131</v>
+      </c>
+      <c r="J186">
+        <v>153</v>
+      </c>
+      <c r="K186">
+        <v>63</v>
+      </c>
+      <c r="L186">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>33</v>
+      </c>
+      <c r="B187" t="s">
+        <v>50</v>
+      </c>
+      <c r="C187">
+        <v>500</v>
+      </c>
+      <c r="D187">
+        <v>14</v>
+      </c>
+      <c r="E187">
+        <v>70</v>
+      </c>
+      <c r="F187">
+        <v>48</v>
+      </c>
+      <c r="G187">
+        <v>28</v>
+      </c>
+      <c r="H187">
+        <v>20</v>
+      </c>
+      <c r="I187">
+        <v>114</v>
+      </c>
+      <c r="J187">
+        <v>169</v>
+      </c>
+      <c r="K187">
+        <v>69</v>
+      </c>
+      <c r="L187">
+        <v>2.5099999999999998</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>12</v>
+      </c>
+      <c r="B188" t="s">
+        <v>39</v>
+      </c>
+      <c r="C188">
+        <v>230</v>
+      </c>
+      <c r="D188">
+        <v>21</v>
+      </c>
+      <c r="E188">
+        <v>72</v>
+      </c>
+      <c r="F188">
+        <v>83</v>
+      </c>
+      <c r="G188">
+        <v>25</v>
+      </c>
+      <c r="H188">
+        <v>25</v>
+      </c>
+      <c r="I188">
+        <v>326</v>
+      </c>
+      <c r="J188">
+        <v>763</v>
+      </c>
+      <c r="K188">
+        <v>116</v>
+      </c>
+      <c r="L188">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>26</v>
+      </c>
+      <c r="B189" t="s">
+        <v>63</v>
+      </c>
+      <c r="C189">
+        <v>115</v>
+      </c>
+      <c r="D189">
+        <v>24</v>
+      </c>
+      <c r="E189">
+        <v>95</v>
+      </c>
+      <c r="F189">
+        <v>65</v>
+      </c>
+      <c r="G189">
+        <v>34</v>
+      </c>
+      <c r="H189">
+        <v>24</v>
+      </c>
+      <c r="I189">
+        <v>338</v>
+      </c>
+      <c r="J189">
+        <v>570</v>
+      </c>
+      <c r="K189">
+        <v>133</v>
+      </c>
+      <c r="L189">
+        <v>5.55</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>46</v>
+      </c>
+      <c r="B190" t="s">
+        <v>23</v>
+      </c>
+      <c r="C190">
+        <v>500</v>
+      </c>
+      <c r="D190">
+        <v>26</v>
+      </c>
+      <c r="E190">
+        <v>90</v>
+      </c>
+      <c r="F190">
+        <v>90</v>
+      </c>
+      <c r="G190">
+        <v>34</v>
+      </c>
+      <c r="H190">
+        <v>61</v>
+      </c>
+      <c r="I190">
+        <v>466</v>
+      </c>
+      <c r="J190">
+        <v>1140</v>
+      </c>
+      <c r="K190">
+        <v>209</v>
+      </c>
+      <c r="L190">
+        <v>7.21</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>42</v>
+      </c>
+      <c r="B191" t="s">
+        <v>18</v>
+      </c>
+      <c r="C191">
+        <v>500</v>
+      </c>
+      <c r="D191">
+        <v>10</v>
+      </c>
+      <c r="E191">
+        <v>67</v>
+      </c>
+      <c r="F191">
+        <v>73</v>
+      </c>
+      <c r="G191">
+        <v>33</v>
+      </c>
+      <c r="H191">
+        <v>5</v>
+      </c>
+      <c r="I191">
+        <v>102</v>
+      </c>
+      <c r="J191">
+        <v>400</v>
+      </c>
+      <c r="K191">
+        <v>45</v>
+      </c>
+      <c r="L191">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>42</v>
+      </c>
+      <c r="B192" t="s">
+        <v>65</v>
+      </c>
+      <c r="C192">
+        <v>115</v>
+      </c>
+      <c r="D192">
+        <v>33</v>
+      </c>
+      <c r="E192">
+        <v>94</v>
+      </c>
+      <c r="F192">
+        <v>88</v>
+      </c>
+      <c r="G192">
+        <v>36</v>
+      </c>
+      <c r="H192">
+        <v>94</v>
+      </c>
+      <c r="I192">
+        <v>517</v>
+      </c>
+      <c r="J192">
+        <v>1280</v>
+      </c>
+      <c r="K192">
+        <v>498</v>
+      </c>
+      <c r="L192">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>40</v>
+      </c>
+      <c r="B193" t="s">
+        <v>62</v>
+      </c>
+      <c r="C193">
+        <v>115</v>
+      </c>
+      <c r="D193">
+        <v>12</v>
+      </c>
+      <c r="E193">
+        <v>59</v>
+      </c>
+      <c r="F193">
+        <v>71</v>
+      </c>
+      <c r="G193">
+        <v>30</v>
+      </c>
+      <c r="H193">
+        <v>22</v>
+      </c>
+      <c r="I193">
+        <v>66</v>
+      </c>
+      <c r="J193">
+        <v>351</v>
+      </c>
+      <c r="K193">
+        <v>46</v>
+      </c>
+      <c r="L193">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>16</v>
+      </c>
+      <c r="B194" t="s">
+        <v>38</v>
+      </c>
+      <c r="C194">
+        <v>115</v>
+      </c>
+      <c r="D194">
+        <v>14</v>
+      </c>
+      <c r="E194">
+        <v>63</v>
+      </c>
+      <c r="F194">
+        <v>47</v>
+      </c>
+      <c r="G194">
+        <v>37</v>
+      </c>
+      <c r="H194">
+        <v>20</v>
+      </c>
+      <c r="I194">
+        <v>26</v>
+      </c>
+      <c r="J194">
+        <v>482</v>
+      </c>
+      <c r="K194">
+        <v>39</v>
+      </c>
+      <c r="L194">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>21</v>
+      </c>
+      <c r="B195" t="s">
+        <v>63</v>
+      </c>
+      <c r="C195">
+        <v>500</v>
+      </c>
+      <c r="D195">
+        <v>23</v>
+      </c>
+      <c r="E195">
+        <v>78</v>
+      </c>
+      <c r="F195">
+        <v>93</v>
+      </c>
+      <c r="G195">
+        <v>34</v>
+      </c>
+      <c r="H195">
+        <v>21</v>
+      </c>
+      <c r="I195">
+        <v>242</v>
+      </c>
+      <c r="J195">
+        <v>723</v>
+      </c>
+      <c r="K195">
+        <v>131</v>
+      </c>
+      <c r="L195">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>26</v>
+      </c>
+      <c r="B196" t="s">
+        <v>59</v>
+      </c>
+      <c r="C196">
+        <v>115</v>
+      </c>
+      <c r="D196">
+        <v>39</v>
+      </c>
+      <c r="E196">
+        <v>90</v>
+      </c>
+      <c r="F196">
+        <v>107</v>
+      </c>
+      <c r="G196">
+        <v>30</v>
+      </c>
+      <c r="H196">
+        <v>67</v>
+      </c>
+      <c r="I196">
+        <v>359</v>
+      </c>
+      <c r="J196">
+        <v>1953</v>
+      </c>
+      <c r="K196">
+        <v>156</v>
+      </c>
+      <c r="L196">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>48</v>
+      </c>
+      <c r="B197" t="s">
+        <v>15</v>
+      </c>
+      <c r="C197">
+        <v>115</v>
+      </c>
+      <c r="D197">
+        <v>24</v>
+      </c>
+      <c r="E197">
+        <v>115</v>
+      </c>
+      <c r="F197">
+        <v>109</v>
+      </c>
+      <c r="G197">
+        <v>31</v>
+      </c>
+      <c r="H197">
+        <v>95</v>
+      </c>
+      <c r="I197">
+        <v>758</v>
+      </c>
+      <c r="J197">
+        <v>1984</v>
+      </c>
+      <c r="K197">
+        <v>180</v>
+      </c>
+      <c r="L197">
+        <v>7.27</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>26</v>
+      </c>
+      <c r="B198" t="s">
+        <v>50</v>
+      </c>
+      <c r="C198">
+        <v>500</v>
+      </c>
+      <c r="D198">
+        <v>10</v>
+      </c>
+      <c r="E198">
+        <v>91</v>
+      </c>
+      <c r="F198">
+        <v>79</v>
+      </c>
+      <c r="G198">
+        <v>38</v>
+      </c>
+      <c r="H198">
+        <v>20</v>
+      </c>
+      <c r="I198">
+        <v>387</v>
+      </c>
+      <c r="J198">
+        <v>984</v>
+      </c>
+      <c r="K198">
+        <v>119</v>
+      </c>
+      <c r="L198">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>19</v>
+      </c>
+      <c r="B199" t="s">
+        <v>61</v>
+      </c>
+      <c r="C199">
+        <v>230</v>
+      </c>
+      <c r="D199">
+        <v>15</v>
+      </c>
+      <c r="E199">
+        <v>96</v>
+      </c>
+      <c r="F199">
+        <v>93</v>
+      </c>
+      <c r="G199">
+        <v>28</v>
+      </c>
+      <c r="H199">
+        <v>42</v>
+      </c>
+      <c r="I199">
+        <v>138</v>
+      </c>
+      <c r="J199">
+        <v>569</v>
+      </c>
+      <c r="K199">
+        <v>141</v>
+      </c>
+      <c r="L199">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>41</v>
+      </c>
+      <c r="B200" t="s">
+        <v>15</v>
+      </c>
+      <c r="C200">
+        <v>500</v>
+      </c>
+      <c r="D200">
+        <v>25</v>
+      </c>
+      <c r="E200">
+        <v>101</v>
+      </c>
+      <c r="F200">
+        <v>101</v>
+      </c>
+      <c r="G200">
+        <v>39</v>
+      </c>
+      <c r="H200">
+        <v>46</v>
+      </c>
+      <c r="I200">
+        <v>961</v>
+      </c>
+      <c r="J200">
+        <v>1432</v>
+      </c>
+      <c r="K200">
+        <v>313</v>
+      </c>
+      <c r="L200">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>43</v>
+      </c>
+      <c r="B201" t="s">
+        <v>23</v>
+      </c>
+      <c r="C201">
+        <v>500</v>
+      </c>
+      <c r="D201">
+        <v>11</v>
+      </c>
+      <c r="E201">
+        <v>61</v>
+      </c>
+      <c r="F201">
+        <v>53</v>
+      </c>
+      <c r="G201">
+        <v>32</v>
+      </c>
+      <c r="H201">
+        <v>16</v>
+      </c>
+      <c r="I201">
+        <v>85</v>
+      </c>
+      <c r="J201">
+        <v>332</v>
+      </c>
+      <c r="K201">
+        <v>74</v>
+      </c>
+      <c r="L201">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>46</v>
+      </c>
+      <c r="B202" t="s">
+        <v>47</v>
+      </c>
+      <c r="C202">
+        <v>230</v>
+      </c>
+      <c r="D202">
+        <v>12</v>
+      </c>
+      <c r="E202">
+        <v>74</v>
+      </c>
+      <c r="F202">
+        <v>53</v>
+      </c>
+      <c r="G202">
+        <v>39</v>
+      </c>
+      <c r="H202">
+        <v>9</v>
+      </c>
+      <c r="I202">
+        <v>21</v>
+      </c>
+      <c r="J202">
+        <v>240</v>
+      </c>
+      <c r="K202">
+        <v>15</v>
+      </c>
+      <c r="L202">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>16</v>
+      </c>
+      <c r="B203" t="s">
+        <v>63</v>
+      </c>
+      <c r="C203">
+        <v>230</v>
+      </c>
+      <c r="D203">
+        <v>37</v>
+      </c>
+      <c r="E203">
+        <v>101</v>
+      </c>
+      <c r="F203">
+        <v>92</v>
+      </c>
+      <c r="G203">
+        <v>40</v>
+      </c>
+      <c r="H203">
+        <v>75</v>
+      </c>
+      <c r="I203">
+        <v>738</v>
+      </c>
+      <c r="J203">
+        <v>1153</v>
+      </c>
+      <c r="K203">
+        <v>496</v>
+      </c>
+      <c r="L203">
+        <v>7.98</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>12</v>
+      </c>
+      <c r="B204" t="s">
+        <v>34</v>
+      </c>
+      <c r="C204">
+        <v>230</v>
+      </c>
+      <c r="D204">
+        <v>18</v>
+      </c>
+      <c r="E204">
+        <v>86</v>
+      </c>
+      <c r="F204">
+        <v>87</v>
+      </c>
+      <c r="G204">
+        <v>32</v>
+      </c>
+      <c r="H204">
+        <v>45</v>
+      </c>
+      <c r="I204">
+        <v>188</v>
+      </c>
+      <c r="J204">
+        <v>541</v>
+      </c>
+      <c r="K204">
+        <v>183</v>
+      </c>
+      <c r="L204">
+        <v>5.89</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>48</v>
+      </c>
+      <c r="B205" t="s">
+        <v>35</v>
+      </c>
+      <c r="C205">
+        <v>500</v>
+      </c>
+      <c r="D205">
+        <v>11</v>
+      </c>
+      <c r="E205">
+        <v>44</v>
+      </c>
+      <c r="F205">
+        <v>65</v>
+      </c>
+      <c r="G205">
+        <v>36</v>
+      </c>
+      <c r="H205">
+        <v>20</v>
+      </c>
+      <c r="I205">
+        <v>108</v>
+      </c>
+      <c r="J205">
+        <v>118</v>
+      </c>
+      <c r="K205">
+        <v>38</v>
+      </c>
+      <c r="L205">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>21</v>
+      </c>
+      <c r="B206" t="s">
+        <v>25</v>
+      </c>
+      <c r="C206">
+        <v>230</v>
+      </c>
+      <c r="D206">
+        <v>33</v>
+      </c>
+      <c r="E206">
+        <v>118</v>
+      </c>
+      <c r="F206">
+        <v>99</v>
+      </c>
+      <c r="G206">
+        <v>33</v>
+      </c>
+      <c r="H206">
+        <v>66</v>
+      </c>
+      <c r="I206">
+        <v>448</v>
+      </c>
+      <c r="J206">
+        <v>841</v>
+      </c>
+      <c r="K206">
+        <v>339</v>
+      </c>
+      <c r="L206">
+        <v>10.16</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>12</v>
+      </c>
+      <c r="B207" t="s">
+        <v>47</v>
+      </c>
+      <c r="C207">
+        <v>500</v>
+      </c>
+      <c r="D207">
+        <v>23</v>
+      </c>
+      <c r="E207">
+        <v>109</v>
+      </c>
+      <c r="F207">
+        <v>106</v>
+      </c>
+      <c r="G207">
+        <v>43</v>
+      </c>
+      <c r="H207">
+        <v>88</v>
+      </c>
+      <c r="I207">
+        <v>860</v>
+      </c>
+      <c r="J207">
+        <v>1086</v>
+      </c>
+      <c r="K207">
+        <v>405</v>
+      </c>
+      <c r="L207">
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>42</v>
+      </c>
+      <c r="B208" t="s">
+        <v>39</v>
+      </c>
+      <c r="C208">
+        <v>115</v>
+      </c>
+      <c r="D208">
+        <v>21</v>
+      </c>
+      <c r="E208">
+        <v>109</v>
+      </c>
+      <c r="F208">
+        <v>117</v>
+      </c>
+      <c r="G208">
+        <v>43</v>
+      </c>
+      <c r="H208">
+        <v>83</v>
+      </c>
+      <c r="I208">
+        <v>466</v>
+      </c>
+      <c r="J208">
+        <v>1599</v>
+      </c>
+      <c r="K208">
+        <v>290</v>
+      </c>
+      <c r="L208">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>26</v>
+      </c>
+      <c r="B209" t="s">
+        <v>35</v>
+      </c>
+      <c r="C209">
+        <v>115</v>
+      </c>
+      <c r="D209">
+        <v>15</v>
+      </c>
+      <c r="E209">
+        <v>80</v>
+      </c>
+      <c r="F209">
+        <v>72</v>
+      </c>
+      <c r="G209">
+        <v>29</v>
+      </c>
+      <c r="H209">
+        <v>31</v>
+      </c>
+      <c r="I209">
+        <v>124</v>
+      </c>
+      <c r="J209">
+        <v>710</v>
+      </c>
+      <c r="K209">
+        <v>182</v>
+      </c>
+      <c r="L209">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>37</v>
+      </c>
+      <c r="B210" t="s">
+        <v>54</v>
+      </c>
+      <c r="C210">
+        <v>500</v>
+      </c>
+      <c r="D210">
+        <v>14</v>
+      </c>
+      <c r="E210">
+        <v>87</v>
+      </c>
+      <c r="F210">
+        <v>89</v>
+      </c>
+      <c r="G210">
+        <v>28</v>
+      </c>
+      <c r="H210">
+        <v>45</v>
+      </c>
+      <c r="I210">
+        <v>314</v>
+      </c>
+      <c r="J210">
+        <v>788</v>
+      </c>
+      <c r="K210">
+        <v>99</v>
+      </c>
+      <c r="L210">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>40</v>
+      </c>
+      <c r="B211" t="s">
+        <v>29</v>
+      </c>
+      <c r="C211">
+        <v>500</v>
+      </c>
+      <c r="D211">
+        <v>5</v>
+      </c>
+      <c r="E211">
+        <v>74</v>
+      </c>
+      <c r="F211">
+        <v>52</v>
+      </c>
+      <c r="G211">
+        <v>32</v>
+      </c>
+      <c r="H211">
+        <v>17</v>
+      </c>
+      <c r="I211">
+        <v>120</v>
+      </c>
+      <c r="J211">
+        <v>272</v>
+      </c>
+      <c r="K211">
+        <v>64</v>
+      </c>
+      <c r="L211">
+        <v>1.79</v>
       </c>
     </row>
   </sheetData>
